--- a/skills/gara-rfp-handoff/assets/template_rfp_handoff.xlsx
+++ b/skills/gara-rfp-handoff/assets/template_rfp_handoff.xlsx
@@ -9,15 +9,16 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Info Sintetiche RFP" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Mappatura Capability" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. Driver di Stima" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Gap Analysis" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Domande Chiarimento" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. Assunzioni" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7. Matrice Profili x Capability" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8. Input Cost Model" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9. Registro Chiarimenti" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10. Nota di Handoff" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Esempi" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requisiti" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. Driver di Stima" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Gap Analysis" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Domande Chiarimento" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. Assunzioni" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7. Matrice Profili x Capability" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8. Input Cost Model" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9. Registro Chiarimenti" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10. Nota di Handoff" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Esempi" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="31">
+  <fonts count="39">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -204,6 +205,47 @@
       <color rgb="00595959"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00374151"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="29">
     <fill>
@@ -348,7 +390,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -426,11 +468,12 @@
         <color rgb="00FECACA"/>
       </bottom>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="143">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -802,6 +845,31 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1252,7 +1320,6 @@
       <c r="B9" s="9" t="n"/>
       <c r="C9" s="10" t="n"/>
     </row>
-    <row r="10"/>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
@@ -1288,7 +1355,6 @@
       <c r="B14" s="14" t="n"/>
       <c r="C14" s="15" t="n"/>
     </row>
-    <row r="15"/>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="19" t="inlineStr">
         <is>
@@ -1333,7 +1399,6 @@
       <c r="B20" s="22" t="n"/>
       <c r="C20" s="23" t="n"/>
     </row>
-    <row r="21"/>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
         <is>
@@ -1396,7 +1461,6 @@
       <c r="B28" s="9" t="n"/>
       <c r="C28" s="10" t="n"/>
     </row>
-    <row r="29"/>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
@@ -1477,7 +1541,6 @@
       <c r="B38" s="9" t="n"/>
       <c r="C38" s="10" t="n"/>
     </row>
-    <row r="39"/>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="32" t="inlineStr">
         <is>
@@ -1549,7 +1612,6 @@
       <c r="B47" s="6" t="n"/>
       <c r="C47" s="7" t="n"/>
     </row>
-    <row r="48"/>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="37" t="inlineStr">
         <is>
@@ -1639,7 +1701,6 @@
       <c r="B58" s="9" t="n"/>
       <c r="C58" s="10" t="n"/>
     </row>
-    <row r="59"/>
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="24" t="inlineStr">
         <is>
@@ -1711,7 +1772,6 @@
       <c r="B67" s="6" t="n"/>
       <c r="C67" s="7" t="n"/>
     </row>
-    <row r="68"/>
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="39" t="inlineStr">
         <is>
@@ -1801,6 +1861,512 @@
   <dimension ref="A1:L33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="35" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="80" t="inlineStr">
+        <is>
+          <t>Registro Chiarimenti — Stato e Impatto sulla Stima</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="81" t="inlineStr">
+        <is>
+          <t>Domande da inviare entro 29/04/2026 ore 12:00 | Ordinate per 'Bloccante per stima' decrescente</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="109" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="109" t="inlineStr">
+        <is>
+          <t>Capability</t>
+        </is>
+      </c>
+      <c r="C3" s="109" t="inlineStr">
+        <is>
+          <t>Categoria</t>
+        </is>
+      </c>
+      <c r="D3" s="109" t="inlineStr">
+        <is>
+          <t>Testo Domanda</t>
+        </is>
+      </c>
+      <c r="E3" s="109" t="inlineStr">
+        <is>
+          <t>Driver che abilita</t>
+        </is>
+      </c>
+      <c r="F3" s="109" t="inlineStr">
+        <is>
+          <t>Prio</t>
+        </is>
+      </c>
+      <c r="G3" s="109" t="inlineStr">
+        <is>
+          <t>Stato</t>
+        </is>
+      </c>
+      <c r="H3" s="109" t="inlineStr">
+        <is>
+          <t>Data Risposta</t>
+        </is>
+      </c>
+      <c r="I3" s="109" t="inlineStr">
+        <is>
+          <t>Sintesi Risposta RAI</t>
+        </is>
+      </c>
+      <c r="J3" s="109" t="inlineStr">
+        <is>
+          <t>Impatto se non risolto</t>
+        </is>
+      </c>
+      <c r="K3" s="109" t="inlineStr">
+        <is>
+          <t>Bloccante per stima</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" s="110" t="n"/>
+      <c r="B4" s="111" t="n"/>
+      <c r="C4" s="112" t="n"/>
+      <c r="D4" s="49" t="n"/>
+      <c r="E4" s="49" t="n"/>
+      <c r="F4" s="140" t="n"/>
+      <c r="G4" s="113" t="n"/>
+      <c r="H4" s="114" t="n"/>
+      <c r="I4" s="49" t="n"/>
+      <c r="J4" s="115" t="n"/>
+      <c r="K4" s="116" t="n"/>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" s="110" t="n"/>
+      <c r="B5" s="111" t="n"/>
+      <c r="C5" s="112" t="n"/>
+      <c r="D5" s="49" t="n"/>
+      <c r="E5" s="49" t="n"/>
+      <c r="F5" s="140" t="n"/>
+      <c r="G5" s="113" t="n"/>
+      <c r="H5" s="114" t="n"/>
+      <c r="I5" s="49" t="n"/>
+      <c r="J5" s="115" t="n"/>
+      <c r="K5" s="116" t="n"/>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="110" t="n"/>
+      <c r="B6" s="111" t="n"/>
+      <c r="C6" s="112" t="n"/>
+      <c r="D6" s="49" t="n"/>
+      <c r="E6" s="49" t="n"/>
+      <c r="F6" s="140" t="n"/>
+      <c r="G6" s="113" t="n"/>
+      <c r="H6" s="114" t="n"/>
+      <c r="I6" s="49" t="n"/>
+      <c r="J6" s="115" t="n"/>
+      <c r="K6" s="116" t="n"/>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="110" t="n"/>
+      <c r="B7" s="111" t="n"/>
+      <c r="C7" s="112" t="n"/>
+      <c r="D7" s="49" t="n"/>
+      <c r="E7" s="49" t="n"/>
+      <c r="F7" s="140" t="n"/>
+      <c r="G7" s="113" t="n"/>
+      <c r="H7" s="114" t="n"/>
+      <c r="I7" s="49" t="n"/>
+      <c r="J7" s="115" t="n"/>
+      <c r="K7" s="116" t="n"/>
+    </row>
+    <row r="8" ht="40" customHeight="1">
+      <c r="A8" s="110" t="n"/>
+      <c r="B8" s="111" t="n"/>
+      <c r="C8" s="112" t="n"/>
+      <c r="D8" s="49" t="n"/>
+      <c r="E8" s="49" t="n"/>
+      <c r="F8" s="140" t="n"/>
+      <c r="G8" s="113" t="n"/>
+      <c r="H8" s="114" t="n"/>
+      <c r="I8" s="49" t="n"/>
+      <c r="J8" s="115" t="n"/>
+      <c r="K8" s="116" t="n"/>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="110" t="n"/>
+      <c r="B9" s="111" t="n"/>
+      <c r="C9" s="112" t="n"/>
+      <c r="D9" s="49" t="n"/>
+      <c r="E9" s="49" t="n"/>
+      <c r="F9" s="140" t="n"/>
+      <c r="G9" s="113" t="n"/>
+      <c r="H9" s="114" t="n"/>
+      <c r="I9" s="49" t="n"/>
+      <c r="J9" s="115" t="n"/>
+      <c r="K9" s="116" t="n"/>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="110" t="n"/>
+      <c r="B10" s="111" t="n"/>
+      <c r="C10" s="112" t="n"/>
+      <c r="D10" s="49" t="n"/>
+      <c r="E10" s="49" t="n"/>
+      <c r="F10" s="140" t="n"/>
+      <c r="G10" s="113" t="n"/>
+      <c r="H10" s="114" t="n"/>
+      <c r="I10" s="49" t="n"/>
+      <c r="J10" s="115" t="n"/>
+      <c r="K10" s="116" t="n"/>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="110" t="n"/>
+      <c r="B11" s="111" t="n"/>
+      <c r="C11" s="112" t="n"/>
+      <c r="D11" s="49" t="n"/>
+      <c r="E11" s="49" t="n"/>
+      <c r="F11" s="140" t="n"/>
+      <c r="G11" s="113" t="n"/>
+      <c r="H11" s="114" t="n"/>
+      <c r="I11" s="49" t="n"/>
+      <c r="J11" s="115" t="n"/>
+      <c r="K11" s="116" t="n"/>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="110" t="n"/>
+      <c r="B12" s="111" t="n"/>
+      <c r="C12" s="112" t="n"/>
+      <c r="D12" s="49" t="n"/>
+      <c r="E12" s="49" t="n"/>
+      <c r="F12" s="140" t="n"/>
+      <c r="G12" s="113" t="n"/>
+      <c r="H12" s="114" t="n"/>
+      <c r="I12" s="49" t="n"/>
+      <c r="J12" s="115" t="n"/>
+      <c r="K12" s="116" t="n"/>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="110" t="n"/>
+      <c r="B13" s="111" t="n"/>
+      <c r="C13" s="112" t="n"/>
+      <c r="D13" s="49" t="n"/>
+      <c r="E13" s="49" t="n"/>
+      <c r="F13" s="140" t="n"/>
+      <c r="G13" s="113" t="n"/>
+      <c r="H13" s="114" t="n"/>
+      <c r="I13" s="49" t="n"/>
+      <c r="J13" s="115" t="n"/>
+      <c r="K13" s="116" t="n"/>
+    </row>
+    <row r="14" ht="40" customHeight="1">
+      <c r="A14" s="110" t="n"/>
+      <c r="B14" s="111" t="n"/>
+      <c r="C14" s="112" t="n"/>
+      <c r="D14" s="49" t="n"/>
+      <c r="E14" s="49" t="n"/>
+      <c r="F14" s="140" t="n"/>
+      <c r="G14" s="113" t="n"/>
+      <c r="H14" s="114" t="n"/>
+      <c r="I14" s="49" t="n"/>
+      <c r="J14" s="115" t="n"/>
+      <c r="K14" s="116" t="n"/>
+    </row>
+    <row r="15" ht="40" customHeight="1">
+      <c r="A15" s="110" t="n"/>
+      <c r="B15" s="111" t="n"/>
+      <c r="C15" s="112" t="n"/>
+      <c r="D15" s="49" t="n"/>
+      <c r="E15" s="49" t="n"/>
+      <c r="F15" s="140" t="n"/>
+      <c r="G15" s="113" t="n"/>
+      <c r="H15" s="114" t="n"/>
+      <c r="I15" s="49" t="n"/>
+      <c r="J15" s="115" t="n"/>
+      <c r="K15" s="116" t="n"/>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="110" t="n"/>
+      <c r="B16" s="111" t="n"/>
+      <c r="C16" s="112" t="n"/>
+      <c r="D16" s="49" t="n"/>
+      <c r="E16" s="49" t="n"/>
+      <c r="F16" s="140" t="n"/>
+      <c r="G16" s="113" t="n"/>
+      <c r="H16" s="114" t="n"/>
+      <c r="I16" s="49" t="n"/>
+      <c r="J16" s="115" t="n"/>
+      <c r="K16" s="116" t="n"/>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="110" t="n"/>
+      <c r="B17" s="111" t="n"/>
+      <c r="C17" s="112" t="n"/>
+      <c r="D17" s="49" t="n"/>
+      <c r="E17" s="49" t="n"/>
+      <c r="F17" s="140" t="n"/>
+      <c r="G17" s="113" t="n"/>
+      <c r="H17" s="114" t="n"/>
+      <c r="I17" s="49" t="n"/>
+      <c r="J17" s="115" t="n"/>
+      <c r="K17" s="116" t="n"/>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="110" t="n"/>
+      <c r="B18" s="111" t="n"/>
+      <c r="C18" s="112" t="n"/>
+      <c r="D18" s="49" t="n"/>
+      <c r="E18" s="49" t="n"/>
+      <c r="F18" s="140" t="n"/>
+      <c r="G18" s="113" t="n"/>
+      <c r="H18" s="114" t="n"/>
+      <c r="I18" s="49" t="n"/>
+      <c r="J18" s="115" t="n"/>
+      <c r="K18" s="116" t="n"/>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="110" t="n"/>
+      <c r="B19" s="111" t="n"/>
+      <c r="C19" s="112" t="n"/>
+      <c r="D19" s="49" t="n"/>
+      <c r="E19" s="49" t="n"/>
+      <c r="F19" s="140" t="n"/>
+      <c r="G19" s="113" t="n"/>
+      <c r="H19" s="114" t="n"/>
+      <c r="I19" s="49" t="n"/>
+      <c r="J19" s="117" t="n"/>
+      <c r="K19" s="118" t="n"/>
+    </row>
+    <row r="20" ht="40" customHeight="1">
+      <c r="A20" s="110" t="n"/>
+      <c r="B20" s="111" t="n"/>
+      <c r="C20" s="112" t="n"/>
+      <c r="D20" s="49" t="n"/>
+      <c r="E20" s="49" t="n"/>
+      <c r="F20" s="140" t="n"/>
+      <c r="G20" s="113" t="n"/>
+      <c r="H20" s="114" t="n"/>
+      <c r="I20" s="49" t="n"/>
+      <c r="J20" s="117" t="n"/>
+      <c r="K20" s="118" t="n"/>
+    </row>
+    <row r="21" ht="40" customHeight="1">
+      <c r="A21" s="110" t="n"/>
+      <c r="B21" s="111" t="n"/>
+      <c r="C21" s="112" t="n"/>
+      <c r="D21" s="49" t="n"/>
+      <c r="E21" s="49" t="n"/>
+      <c r="F21" s="140" t="n"/>
+      <c r="G21" s="113" t="n"/>
+      <c r="H21" s="114" t="n"/>
+      <c r="I21" s="49" t="n"/>
+      <c r="J21" s="117" t="n"/>
+      <c r="K21" s="118" t="n"/>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="110" t="n"/>
+      <c r="B22" s="111" t="n"/>
+      <c r="C22" s="112" t="n"/>
+      <c r="D22" s="49" t="n"/>
+      <c r="E22" s="49" t="n"/>
+      <c r="F22" s="140" t="n"/>
+      <c r="G22" s="113" t="n"/>
+      <c r="H22" s="114" t="n"/>
+      <c r="I22" s="49" t="n"/>
+      <c r="J22" s="117" t="n"/>
+      <c r="K22" s="118" t="n"/>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="110" t="n"/>
+      <c r="B23" s="111" t="n"/>
+      <c r="C23" s="112" t="n"/>
+      <c r="D23" s="49" t="n"/>
+      <c r="E23" s="49" t="n"/>
+      <c r="F23" s="140" t="n"/>
+      <c r="G23" s="113" t="n"/>
+      <c r="H23" s="114" t="n"/>
+      <c r="I23" s="49" t="n"/>
+      <c r="J23" s="117" t="n"/>
+      <c r="K23" s="118" t="n"/>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="110" t="n"/>
+      <c r="B24" s="111" t="n"/>
+      <c r="C24" s="112" t="n"/>
+      <c r="D24" s="49" t="n"/>
+      <c r="E24" s="49" t="n"/>
+      <c r="F24" s="140" t="n"/>
+      <c r="G24" s="113" t="n"/>
+      <c r="H24" s="114" t="n"/>
+      <c r="I24" s="49" t="n"/>
+      <c r="J24" s="117" t="n"/>
+      <c r="K24" s="118" t="n"/>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="110" t="n"/>
+      <c r="B25" s="111" t="n"/>
+      <c r="C25" s="112" t="n"/>
+      <c r="D25" s="49" t="n"/>
+      <c r="E25" s="49" t="n"/>
+      <c r="F25" s="140" t="n"/>
+      <c r="G25" s="113" t="n"/>
+      <c r="H25" s="114" t="n"/>
+      <c r="I25" s="49" t="n"/>
+      <c r="J25" s="117" t="n"/>
+      <c r="K25" s="118" t="n"/>
+    </row>
+    <row r="26" ht="40" customHeight="1">
+      <c r="A26" s="110" t="n"/>
+      <c r="B26" s="111" t="n"/>
+      <c r="C26" s="112" t="n"/>
+      <c r="D26" s="49" t="n"/>
+      <c r="E26" s="49" t="n"/>
+      <c r="F26" s="140" t="n"/>
+      <c r="G26" s="113" t="n"/>
+      <c r="H26" s="114" t="n"/>
+      <c r="I26" s="49" t="n"/>
+      <c r="J26" s="117" t="n"/>
+      <c r="K26" s="118" t="n"/>
+    </row>
+    <row r="27" ht="40" customHeight="1">
+      <c r="A27" s="110" t="n"/>
+      <c r="B27" s="111" t="n"/>
+      <c r="C27" s="112" t="n"/>
+      <c r="D27" s="49" t="n"/>
+      <c r="E27" s="49" t="n"/>
+      <c r="F27" s="140" t="n"/>
+      <c r="G27" s="113" t="n"/>
+      <c r="H27" s="114" t="n"/>
+      <c r="I27" s="49" t="n"/>
+      <c r="J27" s="117" t="n"/>
+      <c r="K27" s="118" t="n"/>
+    </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="110" t="n"/>
+      <c r="B28" s="111" t="n"/>
+      <c r="C28" s="112" t="n"/>
+      <c r="D28" s="49" t="n"/>
+      <c r="E28" s="49" t="n"/>
+      <c r="F28" s="140" t="n"/>
+      <c r="G28" s="113" t="n"/>
+      <c r="H28" s="114" t="n"/>
+      <c r="I28" s="49" t="n"/>
+      <c r="J28" s="117" t="n"/>
+      <c r="K28" s="118" t="n"/>
+    </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="110" t="n"/>
+      <c r="B29" s="111" t="n"/>
+      <c r="C29" s="112" t="n"/>
+      <c r="D29" s="49" t="n"/>
+      <c r="E29" s="49" t="n"/>
+      <c r="F29" s="140" t="n"/>
+      <c r="G29" s="113" t="n"/>
+      <c r="H29" s="114" t="n"/>
+      <c r="I29" s="49" t="n"/>
+      <c r="J29" s="117" t="n"/>
+      <c r="K29" s="118" t="n"/>
+    </row>
+    <row r="30" ht="40" customHeight="1">
+      <c r="A30" s="110" t="n"/>
+      <c r="B30" s="111" t="n"/>
+      <c r="C30" s="112" t="n"/>
+      <c r="D30" s="49" t="n"/>
+      <c r="E30" s="49" t="n"/>
+      <c r="F30" s="140" t="n"/>
+      <c r="G30" s="113" t="n"/>
+      <c r="H30" s="114" t="n"/>
+      <c r="I30" s="49" t="n"/>
+      <c r="J30" s="117" t="n"/>
+      <c r="K30" s="118" t="n"/>
+    </row>
+    <row r="31" ht="40" customHeight="1">
+      <c r="A31" s="110" t="n"/>
+      <c r="B31" s="111" t="n"/>
+      <c r="C31" s="112" t="n"/>
+      <c r="D31" s="49" t="n"/>
+      <c r="E31" s="49" t="n"/>
+      <c r="F31" s="140" t="n"/>
+      <c r="G31" s="113" t="n"/>
+      <c r="H31" s="114" t="n"/>
+      <c r="I31" s="49" t="n"/>
+      <c r="J31" s="113" t="n"/>
+      <c r="K31" s="118" t="n"/>
+    </row>
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="110" t="n"/>
+      <c r="B32" s="111" t="n"/>
+      <c r="C32" s="112" t="n"/>
+      <c r="D32" s="49" t="n"/>
+      <c r="E32" s="49" t="n"/>
+      <c r="F32" s="140" t="n"/>
+      <c r="G32" s="113" t="n"/>
+      <c r="H32" s="114" t="n"/>
+      <c r="I32" s="49" t="n"/>
+      <c r="J32" s="113" t="n"/>
+      <c r="K32" s="118" t="n"/>
+    </row>
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="110" t="n"/>
+      <c r="B33" s="111" t="n"/>
+      <c r="C33" s="112" t="n"/>
+      <c r="D33" s="49" t="n"/>
+      <c r="E33" s="49" t="n"/>
+      <c r="F33" s="140" t="n"/>
+      <c r="G33" s="113" t="n"/>
+      <c r="H33" s="114" t="n"/>
+      <c r="I33" s="49" t="n"/>
+      <c r="J33" s="113" t="n"/>
+      <c r="K33" s="118" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:L1"/>
+  </mergeCells>
+  <dataValidations count="4">
+    <dataValidation sqref="F4:F200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valore non ammesso" error="Valore non ammesso" type="list">
+      <formula1>"1,2,3"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G4:G200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valore non ammesso" error="Valore non ammesso" type="list">
+      <formula1>"Non inviato,Inviato,Risposta ricevuta"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J4:J200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valore non ammesso" error="Valore non ammesso" type="list">
+      <formula1>"ALTO,MEDIO,BASSO"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K4:K200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valore non ammesso" error="Valore non ammesso" type="list">
+      <formula1>"SI,NO"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="90" customWidth="1" min="2" max="2"/>
   </cols>
@@ -1827,53 +2393,104 @@
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="120" t="inlineStr">
+      <c r="A4" s="142" t="inlineStr">
         <is>
           <t>Dati estratti esplicitamente dai documenti di gara, utilizzabili direttamente nel cost model senza ulteriori validazioni.</t>
         </is>
       </c>
+      <c r="C4" s="142" t="n"/>
+      <c r="D4" s="142" t="n"/>
+      <c r="E4" s="142" t="n"/>
+      <c r="F4" s="142" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="121" t="n"/>
-      <c r="B5" s="49" t="n"/>
+      <c r="A5" s="142" t="n"/>
+      <c r="B5" s="142" t="n"/>
+      <c r="C5" s="142" t="n"/>
+      <c r="D5" s="142" t="n"/>
+      <c r="E5" s="142" t="n"/>
+      <c r="F5" s="142" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="121" t="n"/>
-      <c r="B6" s="49" t="n"/>
+      <c r="A6" s="142" t="n"/>
+      <c r="B6" s="142" t="n"/>
+      <c r="C6" s="142" t="n"/>
+      <c r="D6" s="142" t="n"/>
+      <c r="E6" s="142" t="n"/>
+      <c r="F6" s="142" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="121" t="n"/>
-      <c r="B7" s="49" t="n"/>
+      <c r="A7" s="142" t="n"/>
+      <c r="B7" s="142" t="n"/>
+      <c r="C7" s="142" t="n"/>
+      <c r="D7" s="142" t="n"/>
+      <c r="E7" s="142" t="n"/>
+      <c r="F7" s="142" t="n"/>
     </row>
     <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="121" t="n"/>
-      <c r="B8" s="49" t="n"/>
+      <c r="A8" s="142" t="n"/>
+      <c r="B8" s="142" t="n"/>
+      <c r="C8" s="142" t="n"/>
+      <c r="D8" s="142" t="n"/>
+      <c r="E8" s="142" t="n"/>
+      <c r="F8" s="142" t="n"/>
     </row>
     <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="121" t="n"/>
-      <c r="B9" s="49" t="n"/>
+      <c r="A9" s="142" t="n"/>
+      <c r="B9" s="142" t="n"/>
+      <c r="C9" s="142" t="n"/>
+      <c r="D9" s="142" t="n"/>
+      <c r="E9" s="142" t="n"/>
+      <c r="F9" s="142" t="n"/>
     </row>
     <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="121" t="n"/>
-      <c r="B10" s="49" t="n"/>
+      <c r="A10" s="142" t="n"/>
+      <c r="B10" s="142" t="n"/>
+      <c r="C10" s="142" t="n"/>
+      <c r="D10" s="142" t="n"/>
+      <c r="E10" s="142" t="n"/>
+      <c r="F10" s="142" t="n"/>
     </row>
     <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="121" t="n"/>
-      <c r="B11" s="49" t="n"/>
+      <c r="A11" s="142" t="n"/>
+      <c r="B11" s="142" t="n"/>
+      <c r="C11" s="142" t="n"/>
+      <c r="D11" s="142" t="n"/>
+      <c r="E11" s="142" t="n"/>
+      <c r="F11" s="142" t="n"/>
     </row>
     <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="121" t="n"/>
-      <c r="B12" s="49" t="n"/>
+      <c r="A12" s="142" t="n"/>
+      <c r="B12" s="142" t="n"/>
+      <c r="C12" s="142" t="n"/>
+      <c r="D12" s="142" t="n"/>
+      <c r="E12" s="142" t="n"/>
+      <c r="F12" s="142" t="n"/>
     </row>
     <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="121" t="n"/>
-      <c r="B13" s="49" t="n"/>
+      <c r="A13" s="142" t="n"/>
+      <c r="B13" s="142" t="n"/>
+      <c r="C13" s="142" t="n"/>
+      <c r="D13" s="142" t="n"/>
+      <c r="E13" s="142" t="n"/>
+      <c r="F13" s="142" t="n"/>
     </row>
     <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="121" t="n"/>
-      <c r="B14" s="49" t="n"/>
-    </row>
-    <row r="15"/>
+      <c r="A14" s="142" t="n"/>
+      <c r="B14" s="142" t="n"/>
+      <c r="C14" s="142" t="n"/>
+      <c r="D14" s="142" t="n"/>
+      <c r="E14" s="142" t="n"/>
+      <c r="F14" s="142" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="142" t="n"/>
+      <c r="B15" s="142" t="n"/>
+      <c r="C15" s="142" t="n"/>
+      <c r="D15" s="142" t="n"/>
+      <c r="E15" s="142" t="n"/>
+      <c r="F15" s="142" t="n"/>
+    </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="122" t="inlineStr">
         <is>
@@ -1882,45 +2499,88 @@
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="120" t="inlineStr">
+      <c r="A17" s="142" t="inlineStr">
         <is>
           <t>Gap e incoerenze non risolti. Se il cost model procede con assunzioni su questi punti, il rischio finanziario è significativo.</t>
         </is>
       </c>
+      <c r="C17" s="142" t="n"/>
+      <c r="D17" s="142" t="n"/>
+      <c r="E17" s="142" t="n"/>
+      <c r="F17" s="142" t="n"/>
     </row>
     <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="123" t="n"/>
-      <c r="B18" s="49" t="n"/>
+      <c r="A18" s="142" t="n"/>
+      <c r="B18" s="142" t="n"/>
+      <c r="C18" s="142" t="n"/>
+      <c r="D18" s="142" t="n"/>
+      <c r="E18" s="142" t="n"/>
+      <c r="F18" s="142" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="123" t="n"/>
-      <c r="B19" s="49" t="n"/>
+      <c r="A19" s="142" t="n"/>
+      <c r="B19" s="142" t="n"/>
+      <c r="C19" s="142" t="n"/>
+      <c r="D19" s="142" t="n"/>
+      <c r="E19" s="142" t="n"/>
+      <c r="F19" s="142" t="n"/>
     </row>
     <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="123" t="n"/>
-      <c r="B20" s="49" t="n"/>
+      <c r="A20" s="142" t="n"/>
+      <c r="B20" s="142" t="n"/>
+      <c r="C20" s="142" t="n"/>
+      <c r="D20" s="142" t="n"/>
+      <c r="E20" s="142" t="n"/>
+      <c r="F20" s="142" t="n"/>
     </row>
     <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="123" t="n"/>
-      <c r="B21" s="49" t="n"/>
+      <c r="A21" s="142" t="n"/>
+      <c r="B21" s="142" t="n"/>
+      <c r="C21" s="142" t="n"/>
+      <c r="D21" s="142" t="n"/>
+      <c r="E21" s="142" t="n"/>
+      <c r="F21" s="142" t="n"/>
     </row>
     <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="123" t="n"/>
-      <c r="B22" s="49" t="n"/>
+      <c r="A22" s="142" t="n"/>
+      <c r="B22" s="142" t="n"/>
+      <c r="C22" s="142" t="n"/>
+      <c r="D22" s="142" t="n"/>
+      <c r="E22" s="142" t="n"/>
+      <c r="F22" s="142" t="n"/>
     </row>
     <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="123" t="n"/>
-      <c r="B23" s="49" t="n"/>
+      <c r="A23" s="142" t="n"/>
+      <c r="B23" s="142" t="n"/>
+      <c r="C23" s="142" t="n"/>
+      <c r="D23" s="142" t="n"/>
+      <c r="E23" s="142" t="n"/>
+      <c r="F23" s="142" t="n"/>
     </row>
     <row r="24" ht="52" customHeight="1">
-      <c r="A24" s="123" t="n"/>
-      <c r="B24" s="49" t="n"/>
+      <c r="A24" s="142" t="n"/>
+      <c r="B24" s="142" t="n"/>
+      <c r="C24" s="142" t="n"/>
+      <c r="D24" s="142" t="n"/>
+      <c r="E24" s="142" t="n"/>
+      <c r="F24" s="142" t="n"/>
     </row>
     <row r="25" ht="52" customHeight="1">
-      <c r="A25" s="123" t="n"/>
-      <c r="B25" s="49" t="n"/>
-    </row>
-    <row r="26"/>
+      <c r="A25" s="142" t="n"/>
+      <c r="B25" s="142" t="n"/>
+      <c r="C25" s="142" t="n"/>
+      <c r="D25" s="142" t="n"/>
+      <c r="E25" s="142" t="n"/>
+      <c r="F25" s="142" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="142" t="n"/>
+      <c r="B26" s="142" t="n"/>
+      <c r="C26" s="142" t="n"/>
+      <c r="D26" s="142" t="n"/>
+      <c r="E26" s="142" t="n"/>
+      <c r="F26" s="142" t="n"/>
+    </row>
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="124" t="inlineStr">
         <is>
@@ -1929,31 +2589,55 @@
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="120" t="inlineStr">
+      <c r="A28" s="142" t="inlineStr">
         <is>
           <t>Decisioni che il cost modeler o il team di bid deve prendere o far prendere prima di produrre numeri. In ordine di priorità.</t>
         </is>
       </c>
+      <c r="C28" s="142" t="n"/>
+      <c r="D28" s="142" t="n"/>
+      <c r="E28" s="142" t="n"/>
+      <c r="F28" s="142" t="n"/>
     </row>
     <row r="29" ht="52" customHeight="1">
-      <c r="A29" s="125" t="n"/>
-      <c r="B29" s="49" t="n"/>
+      <c r="A29" s="142" t="n"/>
+      <c r="B29" s="142" t="n"/>
+      <c r="C29" s="142" t="n"/>
+      <c r="D29" s="142" t="n"/>
+      <c r="E29" s="142" t="n"/>
+      <c r="F29" s="142" t="n"/>
     </row>
     <row r="30" ht="52" customHeight="1">
-      <c r="A30" s="125" t="n"/>
-      <c r="B30" s="49" t="n"/>
+      <c r="A30" s="142" t="n"/>
+      <c r="B30" s="142" t="n"/>
+      <c r="C30" s="142" t="n"/>
+      <c r="D30" s="142" t="n"/>
+      <c r="E30" s="142" t="n"/>
+      <c r="F30" s="142" t="n"/>
     </row>
     <row r="31" ht="52" customHeight="1">
-      <c r="A31" s="125" t="n"/>
-      <c r="B31" s="49" t="n"/>
+      <c r="A31" s="142" t="n"/>
+      <c r="B31" s="142" t="n"/>
+      <c r="C31" s="142" t="n"/>
+      <c r="D31" s="142" t="n"/>
+      <c r="E31" s="142" t="n"/>
+      <c r="F31" s="142" t="n"/>
     </row>
     <row r="32" ht="52" customHeight="1">
-      <c r="A32" s="125" t="n"/>
-      <c r="B32" s="49" t="n"/>
+      <c r="A32" s="142" t="n"/>
+      <c r="B32" s="142" t="n"/>
+      <c r="C32" s="142" t="n"/>
+      <c r="D32" s="142" t="n"/>
+      <c r="E32" s="142" t="n"/>
+      <c r="F32" s="142" t="n"/>
     </row>
     <row r="33" ht="52" customHeight="1">
-      <c r="A33" s="125" t="n"/>
-      <c r="B33" s="49" t="n"/>
+      <c r="A33" s="142" t="n"/>
+      <c r="B33" s="142" t="n"/>
+      <c r="C33" s="142" t="n"/>
+      <c r="D33" s="142" t="n"/>
+      <c r="E33" s="142" t="n"/>
+      <c r="F33" s="142" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -1970,13 +2654,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H141"/>
+  <dimension ref="A1:H216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3248,11 +3932,785 @@
         </is>
       </c>
     </row>
+    <row r="143">
+      <c r="A143" s="135" t="inlineStr">
+        <is>
+          <t>Sheet Requisiti</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="136" t="inlineStr">
+        <is>
+          <t>Tre esempi tipici: (1) padre+figlio split tecnologico, (2) singolo, (3) cots_product con scope_dettaglio</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="136" t="inlineStr">
+        <is>
+          <t>Esempio 1a: requisito PADRE</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="137" t="inlineStr">
+        <is>
+          <t>col A (ID)</t>
+        </is>
+      </c>
+      <c r="B147" s="138" t="inlineStr">
+        <is>
+          <t>REQ-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="137" t="inlineStr">
+        <is>
+          <t>col B (Tipo)</t>
+        </is>
+      </c>
+      <c r="B148" s="138" t="inlineStr">
+        <is>
+          <t>padre</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="137" t="inlineStr">
+        <is>
+          <t>col C (ID Padre)</t>
+        </is>
+      </c>
+      <c r="B149" s="138" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="137" t="inlineStr">
+        <is>
+          <t>col D (Area Funzionale)</t>
+        </is>
+      </c>
+      <c r="B150" s="138" t="inlineStr">
+        <is>
+          <t>Autenticazione &amp; IAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="137" t="inlineStr">
+        <is>
+          <t>col E (Testo Bando)</t>
+        </is>
+      </c>
+      <c r="B151" s="138" t="inlineStr">
+        <is>
+          <t>Il portale deve consentire l'accesso ai cittadini tramite SPID, CIE e CNS, garantendo SSO con gli applicativi interni.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="137" t="inlineStr">
+        <is>
+          <t>col F (Soluzione Proposta)</t>
+        </is>
+      </c>
+      <c r="B152" s="138" t="inlineStr">
+        <is>
+          <t>Schermate: 1 landing login multi-IdP, 1 callback. API: /auth/idp-redirect, /auth/callback, /session/refresh. Dati: tabella user_session, mapping fiscal_code-&gt;user_id. Processi: federazione via SAML/OIDC con AgID, mapping ruoli.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="137" t="inlineStr">
+        <is>
+          <t>col G (Inferenza)</t>
+        </is>
+      </c>
+      <c r="B153" s="138" t="inlineStr">
+        <is>
+          <t>esplicito</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="137" t="inlineStr">
+        <is>
+          <t>col H (Note Inferenza)</t>
+        </is>
+      </c>
+      <c r="B154" s="138" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="137" t="inlineStr">
+        <is>
+          <t>col I (Rationale Requisito)</t>
+        </is>
+      </c>
+      <c r="B155" s="138" t="inlineStr">
+        <is>
+          <t>Requisito esplicito al Cap. 3.2 del Capitolato. Decomposto in 3 figli per separare i protocolli di federazione (SPID vs CIE/CNS) e l'SSO con applicativi interni che ha effort autonomo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="137" t="inlineStr">
+        <is>
+          <t>col J (Rationale Soluzione)</t>
+        </is>
+      </c>
+      <c r="B156" s="138" t="inlineStr">
+        <is>
+          <t>Pattern federation broker (Keycloak/Auth0) gia consolidato per PA. SAML 2.0 per SPID L2, OIDC per CIE. Token JWT per SSO interno.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="137" t="inlineStr">
+        <is>
+          <t>col K (Categoria Scope)</t>
+        </is>
+      </c>
+      <c r="B157" s="138" t="inlineStr">
+        <is>
+          <t>custom_software</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="137" t="inlineStr">
+        <is>
+          <t>col L (Scope Dettaglio)</t>
+        </is>
+      </c>
+      <c r="B158" s="138" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="137" t="inlineStr">
+        <is>
+          <t>col M (Priorita)</t>
+        </is>
+      </c>
+      <c r="B159" s="138" t="inlineStr">
+        <is>
+          <t>must_have</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="137" t="inlineStr">
+        <is>
+          <t>col N (Certezza)</t>
+        </is>
+      </c>
+      <c r="B160" s="138" t="inlineStr">
+        <is>
+          <t>estratto</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="137" t="inlineStr">
+        <is>
+          <t>col O (Fonte Pag/Sez)</t>
+        </is>
+      </c>
+      <c r="B161" s="138" t="inlineStr">
+        <is>
+          <t>pag. 12, Sez. 3.2 - Identita digitale</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="137" t="inlineStr">
+        <is>
+          <t>col P (Fonte Estratto)</t>
+        </is>
+      </c>
+      <c r="B162" s="138" t="inlineStr">
+        <is>
+          <t>il portale deve consentire l'accesso ai cittadini tramite SPID, CIE e CNS</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="136" t="inlineStr">
+        <is>
+          <t>Esempio 1b: requisito FIGLIO (uno dei 3 della decomposizione)</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="137" t="inlineStr">
+        <is>
+          <t>col A (ID)</t>
+        </is>
+      </c>
+      <c r="B165" s="138" t="inlineStr">
+        <is>
+          <t>REQ-001.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="137" t="inlineStr">
+        <is>
+          <t>col B (Tipo)</t>
+        </is>
+      </c>
+      <c r="B166" s="138" t="inlineStr">
+        <is>
+          <t>figlio</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="137" t="inlineStr">
+        <is>
+          <t>col C (ID Padre)</t>
+        </is>
+      </c>
+      <c r="B167" s="138" t="inlineStr">
+        <is>
+          <t>REQ-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="137" t="inlineStr">
+        <is>
+          <t>col D (Area Funzionale)</t>
+        </is>
+      </c>
+      <c r="B168" s="138" t="inlineStr">
+        <is>
+          <t>Autenticazione &amp; IAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="137" t="inlineStr">
+        <is>
+          <t>col E (Testo Bando)</t>
+        </is>
+      </c>
+      <c r="B169" s="138" t="inlineStr">
+        <is>
+          <t>[da REQ-001] Integrazione con SPID Livello 2 (SAML 2.0).</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="137" t="inlineStr">
+        <is>
+          <t>col F (Soluzione Proposta)</t>
+        </is>
+      </c>
+      <c r="B170" s="138" t="inlineStr">
+        <is>
+          <t>Schermate: pulsante 'Entra con SPID' su landing. API: /auth/spid/redirect, /auth/spid/acs. Dati: metadata SP, attributi minimi SPID. Processi: SAML Web SSO, validazione AssertionConsumerService.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="137" t="inlineStr">
+        <is>
+          <t>col G (Inferenza)</t>
+        </is>
+      </c>
+      <c r="B171" s="138" t="inlineStr">
+        <is>
+          <t>esplicito</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="137" t="inlineStr">
+        <is>
+          <t>col H (Note Inferenza)</t>
+        </is>
+      </c>
+      <c r="B172" s="138" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="137" t="inlineStr">
+        <is>
+          <t>col I (Rationale Requisito)</t>
+        </is>
+      </c>
+      <c r="B173" s="138" t="inlineStr">
+        <is>
+          <t>Sottoinsieme tecnico del padre REQ-001 limitato al canale SPID L2. Separato dal figlio CIE perche i due IdP hanno protocolli, metadata e onboarding distinti.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="137" t="inlineStr">
+        <is>
+          <t>col J (Rationale Soluzione)</t>
+        </is>
+      </c>
+      <c r="B174" s="138" t="inlineStr">
+        <is>
+          <t>Libreria spid-spring-boot-starter (Java) o equivalente Node/.NET. Tempi di onboarding presso AgID circa 4-6 settimane.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="137" t="inlineStr">
+        <is>
+          <t>col K (Categoria Scope)</t>
+        </is>
+      </c>
+      <c r="B175" s="138" t="inlineStr">
+        <is>
+          <t>custom_software</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="137" t="inlineStr">
+        <is>
+          <t>col L (Scope Dettaglio)</t>
+        </is>
+      </c>
+      <c r="B176" s="138" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="137" t="inlineStr">
+        <is>
+          <t>col M (Priorita)</t>
+        </is>
+      </c>
+      <c r="B177" s="138" t="inlineStr">
+        <is>
+          <t>must_have</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="137" t="inlineStr">
+        <is>
+          <t>col N (Certezza)</t>
+        </is>
+      </c>
+      <c r="B178" s="138" t="inlineStr">
+        <is>
+          <t>estratto</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="137" t="inlineStr">
+        <is>
+          <t>col O (Fonte Pag/Sez)</t>
+        </is>
+      </c>
+      <c r="B179" s="138" t="inlineStr">
+        <is>
+          <t>pag. 12, Sez. 3.2.1 - SPID</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="137" t="inlineStr">
+        <is>
+          <t>col P (Fonte Estratto)</t>
+        </is>
+      </c>
+      <c r="B180" s="138" t="inlineStr">
+        <is>
+          <t>Integrazione SPID Livello 2 secondo le specifiche tecniche AgID</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="136" t="inlineStr">
+        <is>
+          <t>Esempio 2: requisito SINGOLO (non decomposto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="137" t="inlineStr">
+        <is>
+          <t>col A (ID)</t>
+        </is>
+      </c>
+      <c r="B183" s="138" t="inlineStr">
+        <is>
+          <t>REQ-007</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="137" t="inlineStr">
+        <is>
+          <t>col B (Tipo)</t>
+        </is>
+      </c>
+      <c r="B184" s="138" t="inlineStr">
+        <is>
+          <t>singolo</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="137" t="inlineStr">
+        <is>
+          <t>col C (ID Padre)</t>
+        </is>
+      </c>
+      <c r="B185" s="138" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="137" t="inlineStr">
+        <is>
+          <t>col D (Area Funzionale)</t>
+        </is>
+      </c>
+      <c r="B186" s="138" t="inlineStr">
+        <is>
+          <t>Accessibilita</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="137" t="inlineStr">
+        <is>
+          <t>col E (Testo Bando)</t>
+        </is>
+      </c>
+      <c r="B187" s="138" t="inlineStr">
+        <is>
+          <t>Tutte le pagine pubbliche devono rispettare le linee guida AgID e WCAG 2.1 livello AA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="137" t="inlineStr">
+        <is>
+          <t>col F (Soluzione Proposta)</t>
+        </is>
+      </c>
+      <c r="B188" s="138" t="inlineStr">
+        <is>
+          <t>Schermate: tutte le viste pubbliche conformi AA. API: nessuna API dedicata. Dati: nessuna struttura dati nuova. Processi: audit accessibilita via WAVE/axe in CI, screening manuale con utenti screen-reader.</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="137" t="inlineStr">
+        <is>
+          <t>col G (Inferenza)</t>
+        </is>
+      </c>
+      <c r="B189" s="138" t="inlineStr">
+        <is>
+          <t>esplicito</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="137" t="inlineStr">
+        <is>
+          <t>col H (Note Inferenza)</t>
+        </is>
+      </c>
+      <c r="B190" s="138" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="137" t="inlineStr">
+        <is>
+          <t>col I (Rationale Requisito)</t>
+        </is>
+      </c>
+      <c r="B191" s="138" t="inlineStr">
+        <is>
+          <t>Vincolo orizzontale, non scomponibile per tecnologia o flusso. Impatta tutte le schermate del portale (~30 viste stimate).</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="137" t="inlineStr">
+        <is>
+          <t>col J (Rationale Soluzione)</t>
+        </is>
+      </c>
+      <c r="B192" s="138" t="inlineStr">
+        <is>
+          <t>Componenti UI da design system AgID o BootstrapItalia (gia conformi AA). Test automatici axe-core in pipeline + audit manuale prima del rilascio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="137" t="inlineStr">
+        <is>
+          <t>col K (Categoria Scope)</t>
+        </is>
+      </c>
+      <c r="B193" s="138" t="inlineStr">
+        <is>
+          <t>custom_software</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="137" t="inlineStr">
+        <is>
+          <t>col L (Scope Dettaglio)</t>
+        </is>
+      </c>
+      <c r="B194" s="138" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="137" t="inlineStr">
+        <is>
+          <t>col M (Priorita)</t>
+        </is>
+      </c>
+      <c r="B195" s="138" t="inlineStr">
+        <is>
+          <t>must_have</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="137" t="inlineStr">
+        <is>
+          <t>col N (Certezza)</t>
+        </is>
+      </c>
+      <c r="B196" s="138" t="inlineStr">
+        <is>
+          <t>estratto</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="137" t="inlineStr">
+        <is>
+          <t>col O (Fonte Pag/Sez)</t>
+        </is>
+      </c>
+      <c r="B197" s="138" t="inlineStr">
+        <is>
+          <t>pag. 28, Sez. 6.4 - Accessibilita</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="137" t="inlineStr">
+        <is>
+          <t>col P (Fonte Estratto)</t>
+        </is>
+      </c>
+      <c r="B198" s="138" t="inlineStr">
+        <is>
+          <t>rispetto delle linee guida AgID e dello standard WCAG 2.1 livello AA</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="136" t="inlineStr">
+        <is>
+          <t>Esempio 3: requisito COTS_PRODUCT (scope_dettaglio popolato)</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="137" t="inlineStr">
+        <is>
+          <t>col A (ID)</t>
+        </is>
+      </c>
+      <c r="B201" s="138" t="inlineStr">
+        <is>
+          <t>REQ-012</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="137" t="inlineStr">
+        <is>
+          <t>col B (Tipo)</t>
+        </is>
+      </c>
+      <c r="B202" s="138" t="inlineStr">
+        <is>
+          <t>singolo</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="137" t="inlineStr">
+        <is>
+          <t>col C (ID Padre)</t>
+        </is>
+      </c>
+      <c r="B203" s="138" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="137" t="inlineStr">
+        <is>
+          <t>col D (Area Funzionale)</t>
+        </is>
+      </c>
+      <c r="B204" s="138" t="inlineStr">
+        <is>
+          <t>Cruscotto Analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="137" t="inlineStr">
+        <is>
+          <t>col E (Testo Bando)</t>
+        </is>
+      </c>
+      <c r="B205" s="138" t="inlineStr">
+        <is>
+          <t>Realizzazione di dashboard direzionali interattive con drill-down e export per i KPI di programma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="137" t="inlineStr">
+        <is>
+          <t>col F (Soluzione Proposta)</t>
+        </is>
+      </c>
+      <c r="B206" s="138" t="inlineStr">
+        <is>
+          <t>Schermate: 5 dashboard direzionali in Power BI (KPI chiave, drill geografico, drill temporale, export PDF/Excel). API: connettori dataset ai DB applicativi. Dati: modello semantico Power BI, dataset incrementale. Processi: refresh schedulato, RLS per ruoli.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="137" t="inlineStr">
+        <is>
+          <t>col G (Inferenza)</t>
+        </is>
+      </c>
+      <c r="B207" s="138" t="inlineStr">
+        <is>
+          <t>stimato</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="137" t="inlineStr">
+        <is>
+          <t>col H (Note Inferenza)</t>
+        </is>
+      </c>
+      <c r="B208" s="138" t="inlineStr">
+        <is>
+          <t>Il documento non cita esplicitamente Power BI ma indica 'piattaforma BI enterprise gia in uso presso il committente'; in fase di chiarimento confermare il prodotto e le licenze disponibili.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="137" t="inlineStr">
+        <is>
+          <t>col I (Rationale Requisito)</t>
+        </is>
+      </c>
+      <c r="B209" s="138" t="inlineStr">
+        <is>
+          <t>Capability dashboard direzionali fuori dal perimetro custom: il committente ha gia piattaforma BI, l'effort e di sviluppo dataset/semantic model + visualizzazioni, non di motore.</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="137" t="inlineStr">
+        <is>
+          <t>col J (Rationale Soluzione)</t>
+        </is>
+      </c>
+      <c r="B210" s="138" t="inlineStr">
+        <is>
+          <t>Power BI Pro/Premium come da prassi PA enterprise. Effort concentrato su modello dati e dashboard, non su engine. Eventuale fallback Tableau o Qlik se non disponibile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="137" t="inlineStr">
+        <is>
+          <t>col K (Categoria Scope)</t>
+        </is>
+      </c>
+      <c r="B211" s="138" t="inlineStr">
+        <is>
+          <t>cots_product</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="137" t="inlineStr">
+        <is>
+          <t>col L (Scope Dettaglio)</t>
+        </is>
+      </c>
+      <c r="B212" s="138" t="inlineStr">
+        <is>
+          <t>Power BI | Microsoft | abbonamento | piattaforma BI enterprise gia adottata dal cliente; effort solo su modellazione e dashboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="137" t="inlineStr">
+        <is>
+          <t>col M (Priorita)</t>
+        </is>
+      </c>
+      <c r="B213" s="138" t="inlineStr">
+        <is>
+          <t>should_have</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="137" t="inlineStr">
+        <is>
+          <t>col N (Certezza)</t>
+        </is>
+      </c>
+      <c r="B214" s="138" t="inlineStr">
+        <is>
+          <t>inferito</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="137" t="inlineStr">
+        <is>
+          <t>col O (Fonte Pag/Sez)</t>
+        </is>
+      </c>
+      <c r="B215" s="138" t="inlineStr">
+        <is>
+          <t>pag. 19, Sez. 4.3 - Cruscotto direzionale</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="137" t="inlineStr">
+        <is>
+          <t>col P (Fonte Estratto)</t>
+        </is>
+      </c>
+      <c r="B216" s="138" t="inlineStr">
+        <is>
+          <t>dashboard direzionali interattive con drill-down e export per i KPI</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="114">
     <mergeCell ref="A77:H77"/>
+    <mergeCell ref="B127:H127"/>
     <mergeCell ref="B40:H40"/>
-    <mergeCell ref="B127:H127"/>
     <mergeCell ref="B49:H49"/>
     <mergeCell ref="B24:H24"/>
     <mergeCell ref="A132:H132"/>
@@ -4107,6 +5565,155 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:P3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="40" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="132" t="inlineStr">
+        <is>
+          <t>Requisiti estratti dalla RFP (popolati da gara-req-extractor v2.0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="133" t="inlineStr">
+        <is>
+          <t>Una riga per ogni elemento dell'array `requisiti` del JSON. Schema v2.0 - 16 campi. NON modificare a mano: tornare a gara-req-extractor se serve aggiornare.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="134" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B3" s="134" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="C3" s="134" t="inlineStr">
+        <is>
+          <t>ID Padre</t>
+        </is>
+      </c>
+      <c r="D3" s="134" t="inlineStr">
+        <is>
+          <t>Area Funzionale</t>
+        </is>
+      </c>
+      <c r="E3" s="134" t="inlineStr">
+        <is>
+          <t>Testo Bando</t>
+        </is>
+      </c>
+      <c r="F3" s="134" t="inlineStr">
+        <is>
+          <t>Soluzione Proposta</t>
+        </is>
+      </c>
+      <c r="G3" s="134" t="inlineStr">
+        <is>
+          <t>Inferenza</t>
+        </is>
+      </c>
+      <c r="H3" s="134" t="inlineStr">
+        <is>
+          <t>Note Inferenza</t>
+        </is>
+      </c>
+      <c r="I3" s="134" t="inlineStr">
+        <is>
+          <t>Rationale Requisito</t>
+        </is>
+      </c>
+      <c r="J3" s="134" t="inlineStr">
+        <is>
+          <t>Rationale Soluzione</t>
+        </is>
+      </c>
+      <c r="K3" s="134" t="inlineStr">
+        <is>
+          <t>Categoria Scope</t>
+        </is>
+      </c>
+      <c r="L3" s="134" t="inlineStr">
+        <is>
+          <t>Scope Dettaglio</t>
+        </is>
+      </c>
+      <c r="M3" s="134" t="inlineStr">
+        <is>
+          <t>Priorita</t>
+        </is>
+      </c>
+      <c r="N3" s="134" t="inlineStr">
+        <is>
+          <t>Certezza</t>
+        </is>
+      </c>
+      <c r="O3" s="134" t="inlineStr">
+        <is>
+          <t>Fonte (Pag/Sez)</t>
+        </is>
+      </c>
+      <c r="P3" s="134" t="inlineStr">
+        <is>
+          <t>Fonte Estratto</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A2:P2"/>
+  </mergeCells>
+  <dataValidations count="5">
+    <dataValidation sqref="B4:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Drop-down obbligatorio" error="Valore non ammesso" type="list">
+      <formula1>"padre,figlio,singolo"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G4:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Drop-down obbligatorio" error="Valore non ammesso" type="list">
+      <formula1>"esplicito,stimato,da_chiarire"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K4:K1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Drop-down obbligatorio" error="Valore non ammesso" type="list">
+      <formula1>"custom_software,cots_product,service_external,out_of_scope"</formula1>
+    </dataValidation>
+    <dataValidation sqref="M4:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Drop-down obbligatorio" error="Valore non ammesso" type="list">
+      <formula1>"must_have,should_have,nice_to_have"</formula1>
+    </dataValidation>
+    <dataValidation sqref="N4:N1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Drop-down obbligatorio" error="Valore non ammesso" type="list">
+      <formula1>"estratto,inferito,assunto"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4669,7 +6276,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4918,7 +6525,6 @@
       <c r="F23" s="57" t="n"/>
       <c r="G23" s="56" t="n"/>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="A25" s="59" t="n"/>
     </row>
@@ -4955,7 +6561,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5024,7 +6630,7 @@
       <c r="C4" s="66" t="n"/>
       <c r="D4" s="49" t="n"/>
       <c r="E4" s="49" t="n"/>
-      <c r="F4" s="55" t="n"/>
+      <c r="F4" s="140" t="n"/>
     </row>
     <row r="5" ht="50" customHeight="1">
       <c r="A5" s="53" t="n"/>
@@ -5032,7 +6638,7 @@
       <c r="C5" s="67" t="n"/>
       <c r="D5" s="49" t="n"/>
       <c r="E5" s="49" t="n"/>
-      <c r="F5" s="55" t="n"/>
+      <c r="F5" s="140" t="n"/>
     </row>
     <row r="6" ht="50" customHeight="1">
       <c r="A6" s="53" t="n"/>
@@ -5040,7 +6646,7 @@
       <c r="C6" s="52" t="n"/>
       <c r="D6" s="49" t="n"/>
       <c r="E6" s="49" t="n"/>
-      <c r="F6" s="57" t="n"/>
+      <c r="F6" s="140" t="n"/>
     </row>
     <row r="7" ht="50" customHeight="1">
       <c r="A7" s="53" t="n"/>
@@ -5048,7 +6654,7 @@
       <c r="C7" s="66" t="n"/>
       <c r="D7" s="49" t="n"/>
       <c r="E7" s="49" t="n"/>
-      <c r="F7" s="57" t="n"/>
+      <c r="F7" s="140" t="n"/>
     </row>
     <row r="8" ht="50" customHeight="1">
       <c r="A8" s="53" t="n"/>
@@ -5056,7 +6662,7 @@
       <c r="C8" s="66" t="n"/>
       <c r="D8" s="49" t="n"/>
       <c r="E8" s="49" t="n"/>
-      <c r="F8" s="55" t="n"/>
+      <c r="F8" s="140" t="n"/>
     </row>
     <row r="9" ht="50" customHeight="1">
       <c r="A9" s="53" t="n"/>
@@ -5064,7 +6670,7 @@
       <c r="C9" s="67" t="n"/>
       <c r="D9" s="49" t="n"/>
       <c r="E9" s="49" t="n"/>
-      <c r="F9" s="55" t="n"/>
+      <c r="F9" s="140" t="n"/>
     </row>
     <row r="10" ht="50" customHeight="1">
       <c r="A10" s="53" t="n"/>
@@ -5072,7 +6678,7 @@
       <c r="C10" s="68" t="n"/>
       <c r="D10" s="49" t="n"/>
       <c r="E10" s="49" t="n"/>
-      <c r="F10" s="55" t="n"/>
+      <c r="F10" s="140" t="n"/>
     </row>
     <row r="11" ht="50" customHeight="1">
       <c r="A11" s="53" t="n"/>
@@ -5080,7 +6686,7 @@
       <c r="C11" s="69" t="n"/>
       <c r="D11" s="49" t="n"/>
       <c r="E11" s="49" t="n"/>
-      <c r="F11" s="57" t="n"/>
+      <c r="F11" s="140" t="n"/>
     </row>
     <row r="12" ht="50" customHeight="1">
       <c r="A12" s="53" t="n"/>
@@ -5088,7 +6694,7 @@
       <c r="C12" s="66" t="n"/>
       <c r="D12" s="49" t="n"/>
       <c r="E12" s="49" t="n"/>
-      <c r="F12" s="55" t="n"/>
+      <c r="F12" s="140" t="n"/>
     </row>
     <row r="13" ht="50" customHeight="1">
       <c r="A13" s="53" t="n"/>
@@ -5096,7 +6702,7 @@
       <c r="C13" s="70" t="n"/>
       <c r="D13" s="49" t="n"/>
       <c r="E13" s="49" t="n"/>
-      <c r="F13" s="55" t="n"/>
+      <c r="F13" s="140" t="n"/>
     </row>
     <row r="14" ht="50" customHeight="1">
       <c r="A14" s="53" t="n"/>
@@ -5104,7 +6710,7 @@
       <c r="C14" s="71" t="n"/>
       <c r="D14" s="49" t="n"/>
       <c r="E14" s="49" t="n"/>
-      <c r="F14" s="57" t="n"/>
+      <c r="F14" s="140" t="n"/>
     </row>
     <row r="15" ht="50" customHeight="1">
       <c r="A15" s="53" t="n"/>
@@ -5112,7 +6718,7 @@
       <c r="C15" s="50" t="n"/>
       <c r="D15" s="49" t="n"/>
       <c r="E15" s="49" t="n"/>
-      <c r="F15" s="57" t="n"/>
+      <c r="F15" s="140" t="n"/>
     </row>
     <row r="16" ht="50" customHeight="1">
       <c r="A16" s="53" t="n"/>
@@ -5120,7 +6726,7 @@
       <c r="C16" s="66" t="n"/>
       <c r="D16" s="49" t="n"/>
       <c r="E16" s="49" t="n"/>
-      <c r="F16" s="55" t="n"/>
+      <c r="F16" s="140" t="n"/>
     </row>
     <row r="17" ht="50" customHeight="1">
       <c r="A17" s="53" t="n"/>
@@ -5128,7 +6734,7 @@
       <c r="C17" s="72" t="n"/>
       <c r="D17" s="49" t="n"/>
       <c r="E17" s="49" t="n"/>
-      <c r="F17" s="55" t="n"/>
+      <c r="F17" s="140" t="n"/>
     </row>
     <row r="18" ht="50" customHeight="1">
       <c r="A18" s="53" t="n"/>
@@ -5136,7 +6742,7 @@
       <c r="C18" s="68" t="n"/>
       <c r="D18" s="49" t="n"/>
       <c r="E18" s="49" t="n"/>
-      <c r="F18" s="55" t="n"/>
+      <c r="F18" s="140" t="n"/>
     </row>
     <row r="19" ht="50" customHeight="1">
       <c r="A19" s="53" t="n"/>
@@ -5144,7 +6750,7 @@
       <c r="C19" s="51" t="n"/>
       <c r="D19" s="49" t="n"/>
       <c r="E19" s="49" t="n"/>
-      <c r="F19" s="55" t="n"/>
+      <c r="F19" s="140" t="n"/>
     </row>
     <row r="20" ht="50" customHeight="1">
       <c r="A20" s="53" t="n"/>
@@ -5152,7 +6758,7 @@
       <c r="C20" s="54" t="n"/>
       <c r="D20" s="49" t="n"/>
       <c r="E20" s="49" t="n"/>
-      <c r="F20" s="55" t="n"/>
+      <c r="F20" s="140" t="n"/>
     </row>
     <row r="21" ht="50" customHeight="1">
       <c r="A21" s="53" t="n"/>
@@ -5160,7 +6766,7 @@
       <c r="C21" s="66" t="n"/>
       <c r="D21" s="49" t="n"/>
       <c r="E21" s="49" t="n"/>
-      <c r="F21" s="57" t="n"/>
+      <c r="F21" s="140" t="n"/>
     </row>
     <row r="22" ht="50" customHeight="1">
       <c r="A22" s="53" t="n"/>
@@ -5168,7 +6774,7 @@
       <c r="C22" s="68" t="n"/>
       <c r="D22" s="49" t="n"/>
       <c r="E22" s="49" t="n"/>
-      <c r="F22" s="55" t="n"/>
+      <c r="F22" s="140" t="n"/>
     </row>
     <row r="23" ht="50" customHeight="1">
       <c r="A23" s="53" t="n"/>
@@ -5176,7 +6782,7 @@
       <c r="C23" s="73" t="n"/>
       <c r="D23" s="49" t="n"/>
       <c r="E23" s="49" t="n"/>
-      <c r="F23" s="57" t="n"/>
+      <c r="F23" s="140" t="n"/>
     </row>
     <row r="24" ht="50" customHeight="1">
       <c r="A24" s="53" t="n"/>
@@ -5184,7 +6790,7 @@
       <c r="C24" s="52" t="n"/>
       <c r="D24" s="49" t="n"/>
       <c r="E24" s="49" t="n"/>
-      <c r="F24" s="57" t="n"/>
+      <c r="F24" s="140" t="n"/>
     </row>
     <row r="25" ht="50" customHeight="1">
       <c r="A25" s="53" t="n"/>
@@ -5192,7 +6798,7 @@
       <c r="C25" s="67" t="n"/>
       <c r="D25" s="49" t="n"/>
       <c r="E25" s="49" t="n"/>
-      <c r="F25" s="57" t="n"/>
+      <c r="F25" s="140" t="n"/>
     </row>
     <row r="26" ht="50" customHeight="1">
       <c r="A26" s="53" t="n"/>
@@ -5200,7 +6806,7 @@
       <c r="C26" s="51" t="n"/>
       <c r="D26" s="49" t="n"/>
       <c r="E26" s="49" t="n"/>
-      <c r="F26" s="57" t="n"/>
+      <c r="F26" s="140" t="n"/>
     </row>
     <row r="27" ht="50" customHeight="1">
       <c r="A27" s="53" t="n"/>
@@ -5208,7 +6814,7 @@
       <c r="C27" s="74" t="n"/>
       <c r="D27" s="49" t="n"/>
       <c r="E27" s="49" t="n"/>
-      <c r="F27" s="57" t="n"/>
+      <c r="F27" s="140" t="n"/>
     </row>
     <row r="28" ht="50" customHeight="1">
       <c r="A28" s="53" t="n"/>
@@ -5216,7 +6822,7 @@
       <c r="C28" s="50" t="n"/>
       <c r="D28" s="49" t="n"/>
       <c r="E28" s="49" t="n"/>
-      <c r="F28" s="55" t="n"/>
+      <c r="F28" s="140" t="n"/>
     </row>
     <row r="29" ht="50" customHeight="1">
       <c r="A29" s="53" t="n"/>
@@ -5224,7 +6830,7 @@
       <c r="C29" s="50" t="n"/>
       <c r="D29" s="49" t="n"/>
       <c r="E29" s="49" t="n"/>
-      <c r="F29" s="55" t="n"/>
+      <c r="F29" s="140" t="n"/>
     </row>
     <row r="30" ht="50" customHeight="1">
       <c r="A30" s="53" t="n"/>
@@ -5232,7 +6838,7 @@
       <c r="C30" s="69" t="n"/>
       <c r="D30" s="49" t="n"/>
       <c r="E30" s="49" t="n"/>
-      <c r="F30" s="57" t="n"/>
+      <c r="F30" s="140" t="n"/>
     </row>
     <row r="31" ht="50" customHeight="1">
       <c r="A31" s="53" t="n"/>
@@ -5240,7 +6846,7 @@
       <c r="C31" s="70" t="n"/>
       <c r="D31" s="49" t="n"/>
       <c r="E31" s="49" t="n"/>
-      <c r="F31" s="75" t="n"/>
+      <c r="F31" s="140" t="n"/>
     </row>
     <row r="32" ht="50" customHeight="1">
       <c r="A32" s="53" t="n"/>
@@ -5248,7 +6854,7 @@
       <c r="C32" s="70" t="n"/>
       <c r="D32" s="49" t="n"/>
       <c r="E32" s="49" t="n"/>
-      <c r="F32" s="75" t="n"/>
+      <c r="F32" s="140" t="n"/>
     </row>
     <row r="33" ht="50" customHeight="1">
       <c r="A33" s="53" t="n"/>
@@ -5256,7 +6862,7 @@
       <c r="C33" s="70" t="n"/>
       <c r="D33" s="49" t="n"/>
       <c r="E33" s="49" t="n"/>
-      <c r="F33" s="75" t="n"/>
+      <c r="F33" s="140" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5272,7 +6878,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5503,7 +7109,6 @@
       <c r="F21" s="49" t="n"/>
       <c r="G21" s="57" t="n"/>
     </row>
-    <row r="22"/>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="91" t="n"/>
     </row>
@@ -5526,7 +7131,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5648,9 +7253,9 @@
       </c>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="84" t="inlineStr">
-        <is>
-          <t>LEGENDA: "P" = Primario (assegnazione esplicita nel documento) | Cella vuota = Non esplicitato nel documento — nessun valore inserito per inferenza</t>
+      <c r="A4" s="139" t="inlineStr">
+        <is>
+          <t>LEGENDA — P-DOC (verde) Primario estratto • P-IPO (giallo) Primario ipotizzato + rationale in col D • S-DOC (azzurro) Supporto estratto • S-IPO (viola) Supporto ipotizzato • cella vuota = N/A</t>
         </is>
       </c>
     </row>
@@ -5666,224 +7271,224 @@
       <c r="B6" s="87" t="n"/>
       <c r="C6" s="86" t="n"/>
       <c r="D6" s="88" t="n"/>
-      <c r="E6" s="89" t="n"/>
-      <c r="F6" s="89" t="n"/>
-      <c r="G6" s="89" t="n"/>
-      <c r="H6" s="89" t="n"/>
-      <c r="I6" s="89" t="n"/>
-      <c r="J6" s="89" t="n"/>
-      <c r="K6" s="89" t="n"/>
-      <c r="L6" s="89" t="n"/>
-      <c r="M6" s="89" t="n"/>
-      <c r="N6" s="89" t="n"/>
+      <c r="E6" s="140" t="n"/>
+      <c r="F6" s="140" t="n"/>
+      <c r="G6" s="140" t="n"/>
+      <c r="H6" s="140" t="n"/>
+      <c r="I6" s="140" t="n"/>
+      <c r="J6" s="140" t="n"/>
+      <c r="K6" s="140" t="n"/>
+      <c r="L6" s="140" t="n"/>
+      <c r="M6" s="140" t="n"/>
+      <c r="N6" s="140" t="n"/>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="86" t="n"/>
       <c r="B7" s="87" t="n"/>
       <c r="C7" s="86" t="n"/>
       <c r="D7" s="88" t="n"/>
-      <c r="E7" s="89" t="n"/>
-      <c r="F7" s="89" t="n"/>
-      <c r="G7" s="90" t="n"/>
-      <c r="H7" s="89" t="n"/>
-      <c r="I7" s="89" t="n"/>
-      <c r="J7" s="89" t="n"/>
-      <c r="K7" s="89" t="n"/>
-      <c r="L7" s="89" t="n"/>
-      <c r="M7" s="89" t="n"/>
-      <c r="N7" s="89" t="n"/>
+      <c r="E7" s="140" t="n"/>
+      <c r="F7" s="140" t="n"/>
+      <c r="G7" s="140" t="n"/>
+      <c r="H7" s="140" t="n"/>
+      <c r="I7" s="140" t="n"/>
+      <c r="J7" s="140" t="n"/>
+      <c r="K7" s="140" t="n"/>
+      <c r="L7" s="140" t="n"/>
+      <c r="M7" s="140" t="n"/>
+      <c r="N7" s="140" t="n"/>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="86" t="n"/>
       <c r="B8" s="87" t="n"/>
       <c r="C8" s="86" t="n"/>
       <c r="D8" s="88" t="n"/>
-      <c r="E8" s="89" t="n"/>
-      <c r="F8" s="89" t="n"/>
-      <c r="G8" s="90" t="n"/>
-      <c r="H8" s="89" t="n"/>
-      <c r="I8" s="89" t="n"/>
-      <c r="J8" s="89" t="n"/>
-      <c r="K8" s="89" t="n"/>
-      <c r="L8" s="89" t="n"/>
-      <c r="M8" s="89" t="n"/>
-      <c r="N8" s="89" t="n"/>
+      <c r="E8" s="140" t="n"/>
+      <c r="F8" s="140" t="n"/>
+      <c r="G8" s="140" t="n"/>
+      <c r="H8" s="140" t="n"/>
+      <c r="I8" s="140" t="n"/>
+      <c r="J8" s="140" t="n"/>
+      <c r="K8" s="140" t="n"/>
+      <c r="L8" s="140" t="n"/>
+      <c r="M8" s="140" t="n"/>
+      <c r="N8" s="140" t="n"/>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="86" t="n"/>
       <c r="B9" s="87" t="n"/>
       <c r="C9" s="86" t="n"/>
       <c r="D9" s="88" t="n"/>
-      <c r="E9" s="89" t="n"/>
-      <c r="F9" s="89" t="n"/>
-      <c r="G9" s="89" t="n"/>
-      <c r="H9" s="89" t="n"/>
-      <c r="I9" s="89" t="n"/>
-      <c r="J9" s="89" t="n"/>
-      <c r="K9" s="89" t="n"/>
-      <c r="L9" s="89" t="n"/>
-      <c r="M9" s="89" t="n"/>
-      <c r="N9" s="89" t="n"/>
+      <c r="E9" s="140" t="n"/>
+      <c r="F9" s="140" t="n"/>
+      <c r="G9" s="140" t="n"/>
+      <c r="H9" s="140" t="n"/>
+      <c r="I9" s="140" t="n"/>
+      <c r="J9" s="140" t="n"/>
+      <c r="K9" s="140" t="n"/>
+      <c r="L9" s="140" t="n"/>
+      <c r="M9" s="140" t="n"/>
+      <c r="N9" s="140" t="n"/>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="86" t="n"/>
       <c r="B10" s="87" t="n"/>
       <c r="C10" s="86" t="n"/>
       <c r="D10" s="88" t="n"/>
-      <c r="E10" s="89" t="n"/>
-      <c r="F10" s="89" t="n"/>
-      <c r="G10" s="89" t="n"/>
-      <c r="H10" s="89" t="n"/>
-      <c r="I10" s="89" t="n"/>
-      <c r="J10" s="89" t="n"/>
-      <c r="K10" s="89" t="n"/>
-      <c r="L10" s="89" t="n"/>
-      <c r="M10" s="89" t="n"/>
-      <c r="N10" s="89" t="n"/>
+      <c r="E10" s="140" t="n"/>
+      <c r="F10" s="140" t="n"/>
+      <c r="G10" s="140" t="n"/>
+      <c r="H10" s="140" t="n"/>
+      <c r="I10" s="140" t="n"/>
+      <c r="J10" s="140" t="n"/>
+      <c r="K10" s="140" t="n"/>
+      <c r="L10" s="140" t="n"/>
+      <c r="M10" s="140" t="n"/>
+      <c r="N10" s="140" t="n"/>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="86" t="n"/>
       <c r="B11" s="87" t="n"/>
       <c r="C11" s="86" t="n"/>
       <c r="D11" s="88" t="n"/>
-      <c r="E11" s="89" t="n"/>
-      <c r="F11" s="89" t="n"/>
-      <c r="G11" s="90" t="n"/>
-      <c r="H11" s="89" t="n"/>
-      <c r="I11" s="89" t="n"/>
-      <c r="J11" s="89" t="n"/>
-      <c r="K11" s="89" t="n"/>
-      <c r="L11" s="89" t="n"/>
-      <c r="M11" s="89" t="n"/>
-      <c r="N11" s="89" t="n"/>
+      <c r="E11" s="140" t="n"/>
+      <c r="F11" s="140" t="n"/>
+      <c r="G11" s="140" t="n"/>
+      <c r="H11" s="140" t="n"/>
+      <c r="I11" s="140" t="n"/>
+      <c r="J11" s="140" t="n"/>
+      <c r="K11" s="140" t="n"/>
+      <c r="L11" s="140" t="n"/>
+      <c r="M11" s="140" t="n"/>
+      <c r="N11" s="140" t="n"/>
     </row>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="86" t="n"/>
       <c r="B12" s="87" t="n"/>
       <c r="C12" s="86" t="n"/>
       <c r="D12" s="88" t="n"/>
-      <c r="E12" s="89" t="n"/>
-      <c r="F12" s="89" t="n"/>
-      <c r="G12" s="90" t="n"/>
-      <c r="H12" s="89" t="n"/>
-      <c r="I12" s="89" t="n"/>
-      <c r="J12" s="89" t="n"/>
-      <c r="K12" s="89" t="n"/>
-      <c r="L12" s="89" t="n"/>
-      <c r="M12" s="89" t="n"/>
-      <c r="N12" s="89" t="n"/>
+      <c r="E12" s="140" t="n"/>
+      <c r="F12" s="140" t="n"/>
+      <c r="G12" s="140" t="n"/>
+      <c r="H12" s="140" t="n"/>
+      <c r="I12" s="140" t="n"/>
+      <c r="J12" s="140" t="n"/>
+      <c r="K12" s="140" t="n"/>
+      <c r="L12" s="140" t="n"/>
+      <c r="M12" s="140" t="n"/>
+      <c r="N12" s="140" t="n"/>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="86" t="n"/>
       <c r="B13" s="87" t="n"/>
       <c r="C13" s="86" t="n"/>
       <c r="D13" s="88" t="n"/>
-      <c r="E13" s="89" t="n"/>
-      <c r="F13" s="89" t="n"/>
-      <c r="G13" s="89" t="n"/>
-      <c r="H13" s="89" t="n"/>
-      <c r="I13" s="89" t="n"/>
-      <c r="J13" s="89" t="n"/>
-      <c r="K13" s="89" t="n"/>
-      <c r="L13" s="89" t="n"/>
-      <c r="M13" s="89" t="n"/>
-      <c r="N13" s="89" t="n"/>
+      <c r="E13" s="140" t="n"/>
+      <c r="F13" s="140" t="n"/>
+      <c r="G13" s="140" t="n"/>
+      <c r="H13" s="140" t="n"/>
+      <c r="I13" s="140" t="n"/>
+      <c r="J13" s="140" t="n"/>
+      <c r="K13" s="140" t="n"/>
+      <c r="L13" s="140" t="n"/>
+      <c r="M13" s="140" t="n"/>
+      <c r="N13" s="140" t="n"/>
     </row>
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="86" t="n"/>
       <c r="B14" s="87" t="n"/>
       <c r="C14" s="86" t="n"/>
       <c r="D14" s="88" t="n"/>
-      <c r="E14" s="89" t="n"/>
-      <c r="F14" s="89" t="n"/>
-      <c r="G14" s="89" t="n"/>
-      <c r="H14" s="89" t="n"/>
-      <c r="I14" s="89" t="n"/>
-      <c r="J14" s="89" t="n"/>
-      <c r="K14" s="89" t="n"/>
-      <c r="L14" s="89" t="n"/>
-      <c r="M14" s="89" t="n"/>
-      <c r="N14" s="89" t="n"/>
+      <c r="E14" s="140" t="n"/>
+      <c r="F14" s="140" t="n"/>
+      <c r="G14" s="140" t="n"/>
+      <c r="H14" s="140" t="n"/>
+      <c r="I14" s="140" t="n"/>
+      <c r="J14" s="140" t="n"/>
+      <c r="K14" s="140" t="n"/>
+      <c r="L14" s="140" t="n"/>
+      <c r="M14" s="140" t="n"/>
+      <c r="N14" s="140" t="n"/>
     </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="86" t="n"/>
       <c r="B15" s="87" t="n"/>
       <c r="C15" s="86" t="n"/>
       <c r="D15" s="88" t="n"/>
-      <c r="E15" s="89" t="n"/>
-      <c r="F15" s="89" t="n"/>
-      <c r="G15" s="90" t="n"/>
-      <c r="H15" s="89" t="n"/>
-      <c r="I15" s="89" t="n"/>
-      <c r="J15" s="89" t="n"/>
-      <c r="K15" s="89" t="n"/>
-      <c r="L15" s="89" t="n"/>
-      <c r="M15" s="89" t="n"/>
-      <c r="N15" s="89" t="n"/>
+      <c r="E15" s="140" t="n"/>
+      <c r="F15" s="140" t="n"/>
+      <c r="G15" s="140" t="n"/>
+      <c r="H15" s="140" t="n"/>
+      <c r="I15" s="140" t="n"/>
+      <c r="J15" s="140" t="n"/>
+      <c r="K15" s="140" t="n"/>
+      <c r="L15" s="140" t="n"/>
+      <c r="M15" s="140" t="n"/>
+      <c r="N15" s="140" t="n"/>
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="86" t="n"/>
       <c r="B16" s="87" t="n"/>
       <c r="C16" s="86" t="n"/>
       <c r="D16" s="88" t="n"/>
-      <c r="E16" s="89" t="n"/>
-      <c r="F16" s="89" t="n"/>
-      <c r="G16" s="90" t="n"/>
-      <c r="H16" s="89" t="n"/>
-      <c r="I16" s="89" t="n"/>
-      <c r="J16" s="89" t="n"/>
-      <c r="K16" s="89" t="n"/>
-      <c r="L16" s="89" t="n"/>
-      <c r="M16" s="89" t="n"/>
-      <c r="N16" s="89" t="n"/>
+      <c r="E16" s="140" t="n"/>
+      <c r="F16" s="140" t="n"/>
+      <c r="G16" s="140" t="n"/>
+      <c r="H16" s="140" t="n"/>
+      <c r="I16" s="140" t="n"/>
+      <c r="J16" s="140" t="n"/>
+      <c r="K16" s="140" t="n"/>
+      <c r="L16" s="140" t="n"/>
+      <c r="M16" s="140" t="n"/>
+      <c r="N16" s="140" t="n"/>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="86" t="n"/>
       <c r="B17" s="87" t="n"/>
       <c r="C17" s="86" t="n"/>
       <c r="D17" s="88" t="n"/>
-      <c r="E17" s="89" t="n"/>
-      <c r="F17" s="89" t="n"/>
-      <c r="G17" s="89" t="n"/>
-      <c r="H17" s="89" t="n"/>
-      <c r="I17" s="89" t="n"/>
-      <c r="J17" s="89" t="n"/>
-      <c r="K17" s="89" t="n"/>
-      <c r="L17" s="89" t="n"/>
-      <c r="M17" s="89" t="n"/>
-      <c r="N17" s="89" t="n"/>
+      <c r="E17" s="140" t="n"/>
+      <c r="F17" s="140" t="n"/>
+      <c r="G17" s="140" t="n"/>
+      <c r="H17" s="140" t="n"/>
+      <c r="I17" s="140" t="n"/>
+      <c r="J17" s="140" t="n"/>
+      <c r="K17" s="140" t="n"/>
+      <c r="L17" s="140" t="n"/>
+      <c r="M17" s="140" t="n"/>
+      <c r="N17" s="140" t="n"/>
     </row>
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="86" t="n"/>
       <c r="B18" s="87" t="n"/>
       <c r="C18" s="86" t="n"/>
       <c r="D18" s="88" t="n"/>
-      <c r="E18" s="89" t="n"/>
-      <c r="F18" s="89" t="n"/>
-      <c r="G18" s="89" t="n"/>
-      <c r="H18" s="89" t="n"/>
-      <c r="I18" s="89" t="n"/>
-      <c r="J18" s="89" t="n"/>
-      <c r="K18" s="89" t="n"/>
-      <c r="L18" s="89" t="n"/>
-      <c r="M18" s="89" t="n"/>
-      <c r="N18" s="89" t="n"/>
+      <c r="E18" s="140" t="n"/>
+      <c r="F18" s="140" t="n"/>
+      <c r="G18" s="140" t="n"/>
+      <c r="H18" s="140" t="n"/>
+      <c r="I18" s="140" t="n"/>
+      <c r="J18" s="140" t="n"/>
+      <c r="K18" s="140" t="n"/>
+      <c r="L18" s="140" t="n"/>
+      <c r="M18" s="140" t="n"/>
+      <c r="N18" s="140" t="n"/>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="86" t="n"/>
       <c r="B19" s="87" t="n"/>
       <c r="C19" s="86" t="n"/>
       <c r="D19" s="88" t="n"/>
-      <c r="E19" s="89" t="n"/>
-      <c r="F19" s="89" t="n"/>
-      <c r="G19" s="90" t="n"/>
-      <c r="H19" s="89" t="n"/>
-      <c r="I19" s="89" t="n"/>
-      <c r="J19" s="89" t="n"/>
-      <c r="K19" s="89" t="n"/>
-      <c r="L19" s="89" t="n"/>
-      <c r="M19" s="89" t="n"/>
-      <c r="N19" s="89" t="n"/>
+      <c r="E19" s="140" t="n"/>
+      <c r="F19" s="140" t="n"/>
+      <c r="G19" s="140" t="n"/>
+      <c r="H19" s="140" t="n"/>
+      <c r="I19" s="140" t="n"/>
+      <c r="J19" s="140" t="n"/>
+      <c r="K19" s="140" t="n"/>
+      <c r="L19" s="140" t="n"/>
+      <c r="M19" s="140" t="n"/>
+      <c r="N19" s="140" t="n"/>
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="86" t="n"/>
@@ -5922,16 +7527,16 @@
       <c r="B22" s="87" t="n"/>
       <c r="C22" s="86" t="n"/>
       <c r="D22" s="88" t="n"/>
-      <c r="E22" s="89" t="n"/>
-      <c r="F22" s="89" t="n"/>
-      <c r="G22" s="89" t="n"/>
-      <c r="H22" s="89" t="n"/>
-      <c r="I22" s="89" t="n"/>
-      <c r="J22" s="89" t="n"/>
-      <c r="K22" s="89" t="n"/>
-      <c r="L22" s="89" t="n"/>
-      <c r="M22" s="89" t="n"/>
-      <c r="N22" s="89" t="n"/>
+      <c r="E22" s="140" t="n"/>
+      <c r="F22" s="140" t="n"/>
+      <c r="G22" s="140" t="n"/>
+      <c r="H22" s="140" t="n"/>
+      <c r="I22" s="140" t="n"/>
+      <c r="J22" s="140" t="n"/>
+      <c r="K22" s="140" t="n"/>
+      <c r="L22" s="140" t="n"/>
+      <c r="M22" s="140" t="n"/>
+      <c r="N22" s="140" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="91" t="inlineStr">
@@ -5939,38 +7544,48 @@
           <t>SERVIZI A RICHIESTA T&amp;M — Profili On-Demand (Capitolato p.14,36)</t>
         </is>
       </c>
+      <c r="E23" s="141" t="n"/>
+      <c r="F23" s="141" t="n"/>
+      <c r="G23" s="141" t="n"/>
+      <c r="H23" s="141" t="n"/>
+      <c r="I23" s="141" t="n"/>
+      <c r="J23" s="141" t="n"/>
+      <c r="K23" s="141" t="n"/>
+      <c r="L23" s="141" t="n"/>
+      <c r="M23" s="141" t="n"/>
+      <c r="N23" s="141" t="n"/>
     </row>
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="92" t="n"/>
       <c r="B24" s="93" t="n"/>
       <c r="C24" s="92" t="n"/>
       <c r="D24" s="94" t="n"/>
-      <c r="E24" s="89" t="n"/>
-      <c r="F24" s="89" t="n"/>
-      <c r="G24" s="89" t="n"/>
-      <c r="H24" s="89" t="n"/>
-      <c r="I24" s="89" t="n"/>
-      <c r="J24" s="89" t="n"/>
-      <c r="K24" s="90" t="n"/>
-      <c r="L24" s="90" t="n"/>
-      <c r="M24" s="90" t="n"/>
-      <c r="N24" s="90" t="n"/>
+      <c r="E24" s="140" t="n"/>
+      <c r="F24" s="140" t="n"/>
+      <c r="G24" s="140" t="n"/>
+      <c r="H24" s="140" t="n"/>
+      <c r="I24" s="140" t="n"/>
+      <c r="J24" s="140" t="n"/>
+      <c r="K24" s="140" t="n"/>
+      <c r="L24" s="140" t="n"/>
+      <c r="M24" s="140" t="n"/>
+      <c r="N24" s="140" t="n"/>
     </row>
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="92" t="n"/>
       <c r="B25" s="93" t="n"/>
       <c r="C25" s="92" t="n"/>
       <c r="D25" s="94" t="n"/>
-      <c r="E25" s="89" t="n"/>
-      <c r="F25" s="89" t="n"/>
-      <c r="G25" s="89" t="n"/>
-      <c r="H25" s="89" t="n"/>
-      <c r="I25" s="89" t="n"/>
-      <c r="J25" s="89" t="n"/>
-      <c r="K25" s="90" t="n"/>
-      <c r="L25" s="90" t="n"/>
-      <c r="M25" s="90" t="n"/>
-      <c r="N25" s="90" t="n"/>
+      <c r="E25" s="140" t="n"/>
+      <c r="F25" s="140" t="n"/>
+      <c r="G25" s="140" t="n"/>
+      <c r="H25" s="140" t="n"/>
+      <c r="I25" s="140" t="n"/>
+      <c r="J25" s="140" t="n"/>
+      <c r="K25" s="140" t="n"/>
+      <c r="L25" s="140" t="n"/>
+      <c r="M25" s="140" t="n"/>
+      <c r="N25" s="140" t="n"/>
     </row>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="92" t="n"/>
@@ -6004,7 +7619,6 @@
       <c r="M27" s="90" t="n"/>
       <c r="N27" s="90" t="n"/>
     </row>
-    <row r="28"/>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="95" t="inlineStr">
         <is>
@@ -6013,13 +7627,11 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="4">
+    <mergeCell ref="A5:N5"/>
+    <mergeCell ref="A4:N4"/>
     <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A4:N4"/>
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A29:N29"/>
-    <mergeCell ref="A5:N5"/>
-    <mergeCell ref="A23:N23"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="A6:A200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valore non ammesso" error="Valore non ammesso" type="list">
@@ -6033,7 +7645,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6125,486 +7737,493 @@
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="99" t="n"/>
-      <c r="B9" s="100" t="n"/>
-      <c r="C9" s="101" t="n"/>
-      <c r="D9" s="101" t="n"/>
-      <c r="E9" s="100" t="n"/>
-      <c r="F9" s="101" t="n"/>
+      <c r="A9" s="142" t="n"/>
+      <c r="B9" s="142" t="n"/>
+      <c r="C9" s="142" t="n"/>
+      <c r="D9" s="142" t="n"/>
+      <c r="E9" s="142" t="n"/>
+      <c r="F9" s="142" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="99" t="n"/>
-      <c r="B10" s="100" t="n"/>
-      <c r="C10" s="101" t="n"/>
-      <c r="D10" s="101" t="n"/>
-      <c r="E10" s="100" t="n"/>
-      <c r="F10" s="101" t="n"/>
+      <c r="A10" s="142" t="n"/>
+      <c r="B10" s="142" t="n"/>
+      <c r="C10" s="142" t="n"/>
+      <c r="D10" s="142" t="n"/>
+      <c r="E10" s="142" t="n"/>
+      <c r="F10" s="142" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="99" t="n"/>
-      <c r="B11" s="100" t="n"/>
-      <c r="C11" s="101" t="n"/>
-      <c r="D11" s="101" t="n"/>
-      <c r="E11" s="100" t="n"/>
-      <c r="F11" s="101" t="n"/>
+      <c r="A11" s="142" t="n"/>
+      <c r="B11" s="142" t="n"/>
+      <c r="C11" s="142" t="n"/>
+      <c r="D11" s="142" t="n"/>
+      <c r="E11" s="142" t="n"/>
+      <c r="F11" s="142" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="99" t="n"/>
-      <c r="B12" s="100" t="n"/>
-      <c r="C12" s="101" t="n"/>
-      <c r="D12" s="101" t="n"/>
-      <c r="E12" s="100" t="n"/>
-      <c r="F12" s="101" t="n"/>
+      <c r="A12" s="142" t="n"/>
+      <c r="B12" s="142" t="n"/>
+      <c r="C12" s="142" t="n"/>
+      <c r="D12" s="142" t="n"/>
+      <c r="E12" s="142" t="n"/>
+      <c r="F12" s="142" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="99" t="n"/>
-      <c r="B13" s="100" t="n"/>
-      <c r="C13" s="101" t="n"/>
-      <c r="D13" s="101" t="n"/>
-      <c r="E13" s="100" t="n"/>
-      <c r="F13" s="101" t="n"/>
+      <c r="A13" s="142" t="n"/>
+      <c r="B13" s="142" t="n"/>
+      <c r="C13" s="142" t="n"/>
+      <c r="D13" s="142" t="n"/>
+      <c r="E13" s="142" t="n"/>
+      <c r="F13" s="142" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="99" t="n"/>
-      <c r="B14" s="100" t="n"/>
-      <c r="C14" s="101" t="n"/>
-      <c r="D14" s="101" t="n"/>
-      <c r="E14" s="100" t="n"/>
-      <c r="F14" s="101" t="n"/>
+      <c r="A14" s="142" t="n"/>
+      <c r="B14" s="142" t="n"/>
+      <c r="C14" s="142" t="n"/>
+      <c r="D14" s="142" t="n"/>
+      <c r="E14" s="142" t="n"/>
+      <c r="F14" s="142" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="99" t="n"/>
-      <c r="B15" s="100" t="n"/>
-      <c r="C15" s="101" t="n"/>
-      <c r="D15" s="101" t="n"/>
-      <c r="E15" s="100" t="n"/>
-      <c r="F15" s="101" t="n"/>
+      <c r="A15" s="142" t="n"/>
+      <c r="B15" s="142" t="n"/>
+      <c r="C15" s="142" t="n"/>
+      <c r="D15" s="142" t="n"/>
+      <c r="E15" s="142" t="n"/>
+      <c r="F15" s="142" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="99" t="n"/>
-      <c r="B16" s="100" t="n"/>
-      <c r="C16" s="101" t="n"/>
-      <c r="D16" s="101" t="n"/>
-      <c r="E16" s="100" t="n"/>
-      <c r="F16" s="101" t="n"/>
+      <c r="A16" s="142" t="n"/>
+      <c r="B16" s="142" t="n"/>
+      <c r="C16" s="142" t="n"/>
+      <c r="D16" s="142" t="n"/>
+      <c r="E16" s="142" t="n"/>
+      <c r="F16" s="142" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="99" t="n"/>
-      <c r="B17" s="100" t="n"/>
-      <c r="C17" s="101" t="n"/>
-      <c r="D17" s="101" t="n"/>
-      <c r="E17" s="100" t="n"/>
-      <c r="F17" s="101" t="n"/>
+      <c r="A17" s="142" t="n"/>
+      <c r="B17" s="142" t="n"/>
+      <c r="C17" s="142" t="n"/>
+      <c r="D17" s="142" t="n"/>
+      <c r="E17" s="142" t="n"/>
+      <c r="F17" s="142" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="99" t="n"/>
-      <c r="B18" s="100" t="n"/>
-      <c r="C18" s="101" t="n"/>
-      <c r="D18" s="101" t="n"/>
-      <c r="E18" s="100" t="n"/>
-      <c r="F18" s="101" t="n"/>
+      <c r="A18" s="142" t="n"/>
+      <c r="B18" s="142" t="n"/>
+      <c r="C18" s="142" t="n"/>
+      <c r="D18" s="142" t="n"/>
+      <c r="E18" s="142" t="n"/>
+      <c r="F18" s="142" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="99" t="n"/>
-      <c r="B19" s="100" t="n"/>
-      <c r="C19" s="101" t="n"/>
-      <c r="D19" s="101" t="n"/>
-      <c r="E19" s="100" t="n"/>
-      <c r="F19" s="101" t="n"/>
+      <c r="A19" s="142" t="n"/>
+      <c r="B19" s="142" t="n"/>
+      <c r="C19" s="142" t="n"/>
+      <c r="D19" s="142" t="n"/>
+      <c r="E19" s="142" t="n"/>
+      <c r="F19" s="142" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="99" t="n"/>
-      <c r="B20" s="100" t="n"/>
-      <c r="C20" s="101" t="n"/>
-      <c r="D20" s="101" t="n"/>
-      <c r="E20" s="100" t="n"/>
-      <c r="F20" s="101" t="n"/>
+      <c r="A20" s="142" t="n"/>
+      <c r="B20" s="142" t="n"/>
+      <c r="C20" s="142" t="n"/>
+      <c r="D20" s="142" t="n"/>
+      <c r="E20" s="142" t="n"/>
+      <c r="F20" s="142" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="99" t="n"/>
-      <c r="B21" s="100" t="n"/>
-      <c r="C21" s="101" t="n"/>
-      <c r="D21" s="101" t="n"/>
-      <c r="E21" s="100" t="n"/>
-      <c r="F21" s="101" t="n"/>
+      <c r="A21" s="142" t="n"/>
+      <c r="B21" s="142" t="n"/>
+      <c r="C21" s="142" t="n"/>
+      <c r="D21" s="142" t="n"/>
+      <c r="E21" s="142" t="n"/>
+      <c r="F21" s="142" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="99" t="n"/>
-      <c r="B22" s="100" t="n"/>
-      <c r="C22" s="101" t="n"/>
-      <c r="D22" s="101" t="n"/>
-      <c r="E22" s="100" t="n"/>
-      <c r="F22" s="101" t="n"/>
+      <c r="A22" s="142" t="n"/>
+      <c r="B22" s="142" t="n"/>
+      <c r="C22" s="142" t="n"/>
+      <c r="D22" s="142" t="n"/>
+      <c r="E22" s="142" t="n"/>
+      <c r="F22" s="142" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="99" t="n"/>
-      <c r="B23" s="100" t="n"/>
-      <c r="C23" s="101" t="n"/>
-      <c r="D23" s="101" t="n"/>
-      <c r="E23" s="100" t="n"/>
-      <c r="F23" s="101" t="n"/>
+      <c r="A23" s="142" t="n"/>
+      <c r="B23" s="142" t="n"/>
+      <c r="C23" s="142" t="n"/>
+      <c r="D23" s="142" t="n"/>
+      <c r="E23" s="142" t="n"/>
+      <c r="F23" s="142" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="99" t="n"/>
-      <c r="B24" s="100" t="n"/>
-      <c r="C24" s="101" t="n"/>
-      <c r="D24" s="101" t="n"/>
-      <c r="E24" s="100" t="n"/>
-      <c r="F24" s="101" t="n"/>
+      <c r="A24" s="142" t="n"/>
+      <c r="B24" s="142" t="n"/>
+      <c r="C24" s="142" t="n"/>
+      <c r="D24" s="142" t="n"/>
+      <c r="E24" s="142" t="n"/>
+      <c r="F24" s="142" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="99" t="n"/>
-      <c r="B25" s="100" t="n"/>
-      <c r="C25" s="101" t="n"/>
-      <c r="D25" s="101" t="n"/>
-      <c r="E25" s="100" t="n"/>
-      <c r="F25" s="101" t="n"/>
+      <c r="A25" s="142" t="n"/>
+      <c r="B25" s="142" t="n"/>
+      <c r="C25" s="142" t="n"/>
+      <c r="D25" s="142" t="n"/>
+      <c r="E25" s="142" t="n"/>
+      <c r="F25" s="142" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="99" t="n"/>
-      <c r="B26" s="100" t="n"/>
-      <c r="C26" s="101" t="n"/>
-      <c r="D26" s="101" t="n"/>
-      <c r="E26" s="100" t="n"/>
-      <c r="F26" s="101" t="n"/>
+      <c r="A26" s="142" t="n"/>
+      <c r="B26" s="142" t="n"/>
+      <c r="C26" s="142" t="n"/>
+      <c r="D26" s="142" t="n"/>
+      <c r="E26" s="142" t="n"/>
+      <c r="F26" s="142" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="99" t="n"/>
-      <c r="B27" s="100" t="n"/>
-      <c r="C27" s="101" t="n"/>
-      <c r="D27" s="101" t="n"/>
-      <c r="E27" s="100" t="n"/>
-      <c r="F27" s="101" t="n"/>
+      <c r="A27" s="142" t="n"/>
+      <c r="B27" s="142" t="n"/>
+      <c r="C27" s="142" t="n"/>
+      <c r="D27" s="142" t="n"/>
+      <c r="E27" s="142" t="n"/>
+      <c r="F27" s="142" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="99" t="n"/>
-      <c r="B28" s="100" t="n"/>
-      <c r="C28" s="101" t="n"/>
-      <c r="D28" s="101" t="n"/>
-      <c r="E28" s="100" t="n"/>
-      <c r="F28" s="101" t="n"/>
+      <c r="A28" s="142" t="n"/>
+      <c r="B28" s="142" t="n"/>
+      <c r="C28" s="142" t="n"/>
+      <c r="D28" s="142" t="n"/>
+      <c r="E28" s="142" t="n"/>
+      <c r="F28" s="142" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="99" t="n"/>
-      <c r="B29" s="100" t="n"/>
-      <c r="C29" s="101" t="n"/>
-      <c r="D29" s="101" t="n"/>
-      <c r="E29" s="100" t="n"/>
-      <c r="F29" s="101" t="n"/>
+      <c r="A29" s="142" t="n"/>
+      <c r="B29" s="142" t="n"/>
+      <c r="C29" s="142" t="n"/>
+      <c r="D29" s="142" t="n"/>
+      <c r="E29" s="142" t="n"/>
+      <c r="F29" s="142" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="99" t="n"/>
-      <c r="B30" s="100" t="n"/>
-      <c r="C30" s="101" t="n"/>
-      <c r="D30" s="101" t="n"/>
-      <c r="E30" s="100" t="n"/>
-      <c r="F30" s="101" t="n"/>
+      <c r="A30" s="142" t="n"/>
+      <c r="B30" s="142" t="n"/>
+      <c r="C30" s="142" t="n"/>
+      <c r="D30" s="142" t="n"/>
+      <c r="E30" s="142" t="n"/>
+      <c r="F30" s="142" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="99" t="n"/>
-      <c r="B31" s="100" t="n"/>
-      <c r="C31" s="101" t="n"/>
-      <c r="D31" s="101" t="n"/>
-      <c r="E31" s="100" t="n"/>
-      <c r="F31" s="101" t="n"/>
+      <c r="A31" s="142" t="n"/>
+      <c r="B31" s="142" t="n"/>
+      <c r="C31" s="142" t="n"/>
+      <c r="D31" s="142" t="n"/>
+      <c r="E31" s="142" t="n"/>
+      <c r="F31" s="142" t="n"/>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="99" t="n"/>
-      <c r="B32" s="100" t="n"/>
-      <c r="C32" s="101" t="n"/>
-      <c r="D32" s="101" t="n"/>
-      <c r="E32" s="100" t="n"/>
-      <c r="F32" s="101" t="n"/>
+      <c r="A32" s="142" t="n"/>
+      <c r="B32" s="142" t="n"/>
+      <c r="C32" s="142" t="n"/>
+      <c r="D32" s="142" t="n"/>
+      <c r="E32" s="142" t="n"/>
+      <c r="F32" s="142" t="n"/>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="99" t="n"/>
-      <c r="B33" s="100" t="n"/>
-      <c r="C33" s="101" t="n"/>
-      <c r="D33" s="101" t="n"/>
-      <c r="E33" s="100" t="n"/>
-      <c r="F33" s="101" t="n"/>
+      <c r="A33" s="142" t="n"/>
+      <c r="B33" s="142" t="n"/>
+      <c r="C33" s="142" t="n"/>
+      <c r="D33" s="142" t="n"/>
+      <c r="E33" s="142" t="n"/>
+      <c r="F33" s="142" t="n"/>
     </row>
     <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="99" t="n"/>
-      <c r="B34" s="100" t="n"/>
-      <c r="C34" s="101" t="n"/>
-      <c r="D34" s="101" t="n"/>
-      <c r="E34" s="100" t="n"/>
-      <c r="F34" s="101" t="n"/>
+      <c r="A34" s="142" t="n"/>
+      <c r="B34" s="142" t="n"/>
+      <c r="C34" s="142" t="n"/>
+      <c r="D34" s="142" t="n"/>
+      <c r="E34" s="142" t="n"/>
+      <c r="F34" s="142" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="99" t="n"/>
-      <c r="B35" s="100" t="n"/>
-      <c r="C35" s="101" t="n"/>
-      <c r="D35" s="101" t="n"/>
-      <c r="E35" s="100" t="n"/>
-      <c r="F35" s="101" t="n"/>
+      <c r="A35" s="142" t="n"/>
+      <c r="B35" s="142" t="n"/>
+      <c r="C35" s="142" t="n"/>
+      <c r="D35" s="142" t="n"/>
+      <c r="E35" s="142" t="n"/>
+      <c r="F35" s="142" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="99" t="n"/>
-      <c r="B36" s="100" t="n"/>
-      <c r="C36" s="101" t="n"/>
-      <c r="D36" s="101" t="n"/>
-      <c r="E36" s="100" t="n"/>
-      <c r="F36" s="101" t="n"/>
+      <c r="A36" s="142" t="n"/>
+      <c r="B36" s="142" t="n"/>
+      <c r="C36" s="142" t="n"/>
+      <c r="D36" s="142" t="n"/>
+      <c r="E36" s="142" t="n"/>
+      <c r="F36" s="142" t="n"/>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="99" t="n"/>
-      <c r="B37" s="100" t="n"/>
-      <c r="C37" s="101" t="n"/>
-      <c r="D37" s="101" t="n"/>
-      <c r="E37" s="100" t="n"/>
-      <c r="F37" s="101" t="n"/>
+      <c r="A37" s="142" t="n"/>
+      <c r="B37" s="142" t="n"/>
+      <c r="C37" s="142" t="n"/>
+      <c r="D37" s="142" t="n"/>
+      <c r="E37" s="142" t="n"/>
+      <c r="F37" s="142" t="n"/>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="99" t="n"/>
-      <c r="B38" s="100" t="n"/>
-      <c r="C38" s="101" t="n"/>
-      <c r="D38" s="101" t="n"/>
-      <c r="E38" s="100" t="n"/>
-      <c r="F38" s="101" t="n"/>
+      <c r="A38" s="142" t="n"/>
+      <c r="B38" s="142" t="n"/>
+      <c r="C38" s="142" t="n"/>
+      <c r="D38" s="142" t="n"/>
+      <c r="E38" s="142" t="n"/>
+      <c r="F38" s="142" t="n"/>
     </row>
     <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="99" t="n"/>
-      <c r="B39" s="100" t="n"/>
-      <c r="C39" s="101" t="n"/>
-      <c r="D39" s="101" t="n"/>
-      <c r="E39" s="100" t="n"/>
-      <c r="F39" s="101" t="n"/>
+      <c r="A39" s="142" t="n"/>
+      <c r="B39" s="142" t="n"/>
+      <c r="C39" s="142" t="n"/>
+      <c r="D39" s="142" t="n"/>
+      <c r="E39" s="142" t="n"/>
+      <c r="F39" s="142" t="n"/>
     </row>
     <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="99" t="n"/>
-      <c r="B40" s="100" t="n"/>
-      <c r="C40" s="101" t="n"/>
-      <c r="D40" s="101" t="n"/>
-      <c r="E40" s="100" t="n"/>
-      <c r="F40" s="101" t="n"/>
+      <c r="A40" s="142" t="n"/>
+      <c r="B40" s="142" t="n"/>
+      <c r="C40" s="142" t="n"/>
+      <c r="D40" s="142" t="n"/>
+      <c r="E40" s="142" t="n"/>
+      <c r="F40" s="142" t="n"/>
     </row>
     <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="99" t="n"/>
-      <c r="B41" s="100" t="n"/>
-      <c r="C41" s="101" t="n"/>
-      <c r="D41" s="101" t="n"/>
-      <c r="E41" s="100" t="n"/>
-      <c r="F41" s="101" t="n"/>
+      <c r="A41" s="142" t="n"/>
+      <c r="B41" s="142" t="n"/>
+      <c r="C41" s="142" t="n"/>
+      <c r="D41" s="142" t="n"/>
+      <c r="E41" s="142" t="n"/>
+      <c r="F41" s="142" t="n"/>
     </row>
     <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="99" t="n"/>
-      <c r="B42" s="100" t="n"/>
-      <c r="C42" s="101" t="n"/>
-      <c r="D42" s="101" t="n"/>
-      <c r="E42" s="100" t="n"/>
-      <c r="F42" s="101" t="n"/>
+      <c r="A42" s="142" t="n"/>
+      <c r="B42" s="142" t="n"/>
+      <c r="C42" s="142" t="n"/>
+      <c r="D42" s="142" t="n"/>
+      <c r="E42" s="142" t="n"/>
+      <c r="F42" s="142" t="n"/>
     </row>
     <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="99" t="n"/>
-      <c r="B43" s="100" t="n"/>
-      <c r="C43" s="101" t="n"/>
-      <c r="D43" s="101" t="n"/>
-      <c r="E43" s="100" t="n"/>
-      <c r="F43" s="101" t="n"/>
+      <c r="A43" s="142" t="n"/>
+      <c r="B43" s="142" t="n"/>
+      <c r="C43" s="142" t="n"/>
+      <c r="D43" s="142" t="n"/>
+      <c r="E43" s="142" t="n"/>
+      <c r="F43" s="142" t="n"/>
     </row>
     <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="99" t="n"/>
-      <c r="B44" s="100" t="n"/>
-      <c r="C44" s="101" t="n"/>
-      <c r="D44" s="101" t="n"/>
-      <c r="E44" s="100" t="n"/>
-      <c r="F44" s="101" t="n"/>
+      <c r="A44" s="142" t="n"/>
+      <c r="B44" s="142" t="n"/>
+      <c r="C44" s="142" t="n"/>
+      <c r="D44" s="142" t="n"/>
+      <c r="E44" s="142" t="n"/>
+      <c r="F44" s="142" t="n"/>
     </row>
     <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="99" t="n"/>
-      <c r="B45" s="100" t="n"/>
-      <c r="C45" s="101" t="n"/>
-      <c r="D45" s="101" t="n"/>
-      <c r="E45" s="100" t="n"/>
-      <c r="F45" s="101" t="n"/>
+      <c r="A45" s="142" t="n"/>
+      <c r="B45" s="142" t="n"/>
+      <c r="C45" s="142" t="n"/>
+      <c r="D45" s="142" t="n"/>
+      <c r="E45" s="142" t="n"/>
+      <c r="F45" s="142" t="n"/>
     </row>
     <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="99" t="n"/>
-      <c r="B46" s="100" t="n"/>
-      <c r="C46" s="101" t="n"/>
-      <c r="D46" s="101" t="n"/>
-      <c r="E46" s="100" t="n"/>
-      <c r="F46" s="101" t="n"/>
+      <c r="A46" s="142" t="n"/>
+      <c r="B46" s="142" t="n"/>
+      <c r="C46" s="142" t="n"/>
+      <c r="D46" s="142" t="n"/>
+      <c r="E46" s="142" t="n"/>
+      <c r="F46" s="142" t="n"/>
     </row>
     <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="99" t="n"/>
-      <c r="B47" s="100" t="n"/>
-      <c r="C47" s="101" t="n"/>
-      <c r="D47" s="101" t="n"/>
-      <c r="E47" s="100" t="n"/>
-      <c r="F47" s="101" t="n"/>
+      <c r="A47" s="142" t="n"/>
+      <c r="B47" s="142" t="n"/>
+      <c r="C47" s="142" t="n"/>
+      <c r="D47" s="142" t="n"/>
+      <c r="E47" s="142" t="n"/>
+      <c r="F47" s="142" t="n"/>
     </row>
     <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="99" t="n"/>
-      <c r="B48" s="100" t="n"/>
-      <c r="C48" s="101" t="n"/>
-      <c r="D48" s="101" t="n"/>
-      <c r="E48" s="100" t="n"/>
-      <c r="F48" s="101" t="n"/>
+      <c r="A48" s="142" t="n"/>
+      <c r="B48" s="142" t="n"/>
+      <c r="C48" s="142" t="n"/>
+      <c r="D48" s="142" t="n"/>
+      <c r="E48" s="142" t="n"/>
+      <c r="F48" s="142" t="n"/>
     </row>
     <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="99" t="n"/>
-      <c r="B49" s="100" t="n"/>
-      <c r="C49" s="101" t="n"/>
-      <c r="D49" s="101" t="n"/>
-      <c r="E49" s="100" t="n"/>
-      <c r="F49" s="101" t="n"/>
+      <c r="A49" s="142" t="n"/>
+      <c r="B49" s="142" t="n"/>
+      <c r="C49" s="142" t="n"/>
+      <c r="D49" s="142" t="n"/>
+      <c r="E49" s="142" t="n"/>
+      <c r="F49" s="142" t="n"/>
     </row>
     <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="99" t="n"/>
-      <c r="B50" s="100" t="n"/>
-      <c r="C50" s="101" t="n"/>
-      <c r="D50" s="101" t="n"/>
-      <c r="E50" s="100" t="n"/>
-      <c r="F50" s="101" t="n"/>
+      <c r="A50" s="142" t="n"/>
+      <c r="B50" s="142" t="n"/>
+      <c r="C50" s="142" t="n"/>
+      <c r="D50" s="142" t="n"/>
+      <c r="E50" s="142" t="n"/>
+      <c r="F50" s="142" t="n"/>
     </row>
     <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="99" t="n"/>
-      <c r="B51" s="100" t="n"/>
-      <c r="C51" s="101" t="n"/>
-      <c r="D51" s="101" t="n"/>
-      <c r="E51" s="100" t="n"/>
-      <c r="F51" s="101" t="n"/>
+      <c r="A51" s="142" t="n"/>
+      <c r="B51" s="142" t="n"/>
+      <c r="C51" s="142" t="n"/>
+      <c r="D51" s="142" t="n"/>
+      <c r="E51" s="142" t="n"/>
+      <c r="F51" s="142" t="n"/>
     </row>
     <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="99" t="n"/>
-      <c r="B52" s="100" t="n"/>
-      <c r="C52" s="101" t="n"/>
-      <c r="D52" s="101" t="n"/>
-      <c r="E52" s="100" t="n"/>
-      <c r="F52" s="101" t="n"/>
+      <c r="A52" s="142" t="n"/>
+      <c r="B52" s="142" t="n"/>
+      <c r="C52" s="142" t="n"/>
+      <c r="D52" s="142" t="n"/>
+      <c r="E52" s="142" t="n"/>
+      <c r="F52" s="142" t="n"/>
     </row>
     <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="99" t="n"/>
-      <c r="B53" s="100" t="n"/>
-      <c r="C53" s="101" t="n"/>
-      <c r="D53" s="101" t="n"/>
-      <c r="E53" s="100" t="n"/>
-      <c r="F53" s="101" t="n"/>
+      <c r="A53" s="142" t="n"/>
+      <c r="B53" s="142" t="n"/>
+      <c r="C53" s="142" t="n"/>
+      <c r="D53" s="142" t="n"/>
+      <c r="E53" s="142" t="n"/>
+      <c r="F53" s="142" t="n"/>
     </row>
     <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="99" t="n"/>
-      <c r="B54" s="100" t="n"/>
-      <c r="C54" s="101" t="n"/>
-      <c r="D54" s="101" t="n"/>
-      <c r="E54" s="100" t="n"/>
-      <c r="F54" s="101" t="n"/>
+      <c r="A54" s="142" t="n"/>
+      <c r="B54" s="142" t="n"/>
+      <c r="C54" s="142" t="n"/>
+      <c r="D54" s="142" t="n"/>
+      <c r="E54" s="142" t="n"/>
+      <c r="F54" s="142" t="n"/>
     </row>
     <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="99" t="n"/>
-      <c r="B55" s="100" t="n"/>
-      <c r="C55" s="101" t="n"/>
-      <c r="D55" s="101" t="n"/>
-      <c r="E55" s="100" t="n"/>
-      <c r="F55" s="101" t="n"/>
+      <c r="A55" s="142" t="n"/>
+      <c r="B55" s="142" t="n"/>
+      <c r="C55" s="142" t="n"/>
+      <c r="D55" s="142" t="n"/>
+      <c r="E55" s="142" t="n"/>
+      <c r="F55" s="142" t="n"/>
     </row>
     <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="99" t="n"/>
-      <c r="B56" s="100" t="n"/>
-      <c r="C56" s="101" t="n"/>
-      <c r="D56" s="101" t="n"/>
-      <c r="E56" s="100" t="n"/>
-      <c r="F56" s="101" t="n"/>
+      <c r="A56" s="142" t="n"/>
+      <c r="B56" s="142" t="n"/>
+      <c r="C56" s="142" t="n"/>
+      <c r="D56" s="142" t="n"/>
+      <c r="E56" s="142" t="n"/>
+      <c r="F56" s="142" t="n"/>
     </row>
     <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="99" t="n"/>
-      <c r="B57" s="100" t="n"/>
-      <c r="C57" s="101" t="n"/>
-      <c r="D57" s="101" t="n"/>
-      <c r="E57" s="100" t="n"/>
-      <c r="F57" s="101" t="n"/>
+      <c r="A57" s="142" t="n"/>
+      <c r="B57" s="142" t="n"/>
+      <c r="C57" s="142" t="n"/>
+      <c r="D57" s="142" t="n"/>
+      <c r="E57" s="142" t="n"/>
+      <c r="F57" s="142" t="n"/>
     </row>
     <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="99" t="n"/>
-      <c r="B58" s="100" t="n"/>
-      <c r="C58" s="101" t="n"/>
-      <c r="D58" s="101" t="n"/>
-      <c r="E58" s="100" t="n"/>
-      <c r="F58" s="101" t="n"/>
+      <c r="A58" s="142" t="n"/>
+      <c r="B58" s="142" t="n"/>
+      <c r="C58" s="142" t="n"/>
+      <c r="D58" s="142" t="n"/>
+      <c r="E58" s="142" t="n"/>
+      <c r="F58" s="142" t="n"/>
     </row>
     <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="99" t="n"/>
-      <c r="B59" s="100" t="n"/>
-      <c r="C59" s="101" t="n"/>
-      <c r="D59" s="101" t="n"/>
-      <c r="E59" s="100" t="n"/>
-      <c r="F59" s="101" t="n"/>
+      <c r="A59" s="142" t="n"/>
+      <c r="B59" s="142" t="n"/>
+      <c r="C59" s="142" t="n"/>
+      <c r="D59" s="142" t="n"/>
+      <c r="E59" s="142" t="n"/>
+      <c r="F59" s="142" t="n"/>
     </row>
     <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="99" t="n"/>
-      <c r="B60" s="100" t="n"/>
-      <c r="C60" s="101" t="n"/>
-      <c r="D60" s="101" t="n"/>
-      <c r="E60" s="100" t="n"/>
-      <c r="F60" s="101" t="n"/>
+      <c r="A60" s="142" t="n"/>
+      <c r="B60" s="142" t="n"/>
+      <c r="C60" s="142" t="n"/>
+      <c r="D60" s="142" t="n"/>
+      <c r="E60" s="142" t="n"/>
+      <c r="F60" s="142" t="n"/>
     </row>
     <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="99" t="n"/>
-      <c r="B61" s="100" t="n"/>
-      <c r="C61" s="101" t="n"/>
-      <c r="D61" s="101" t="n"/>
-      <c r="E61" s="100" t="n"/>
-      <c r="F61" s="101" t="n"/>
+      <c r="A61" s="142" t="n"/>
+      <c r="B61" s="142" t="n"/>
+      <c r="C61" s="142" t="n"/>
+      <c r="D61" s="142" t="n"/>
+      <c r="E61" s="142" t="n"/>
+      <c r="F61" s="142" t="n"/>
     </row>
     <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="99" t="n"/>
-      <c r="B62" s="100" t="n"/>
-      <c r="C62" s="101" t="n"/>
-      <c r="D62" s="101" t="n"/>
-      <c r="E62" s="100" t="n"/>
-      <c r="F62" s="101" t="n"/>
+      <c r="A62" s="142" t="n"/>
+      <c r="B62" s="142" t="n"/>
+      <c r="C62" s="142" t="n"/>
+      <c r="D62" s="142" t="n"/>
+      <c r="E62" s="142" t="n"/>
+      <c r="F62" s="142" t="n"/>
     </row>
     <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="99" t="n"/>
-      <c r="B63" s="100" t="n"/>
-      <c r="C63" s="101" t="n"/>
-      <c r="D63" s="101" t="n"/>
-      <c r="E63" s="100" t="n"/>
-      <c r="F63" s="101" t="n"/>
+      <c r="A63" s="142" t="n"/>
+      <c r="B63" s="142" t="n"/>
+      <c r="C63" s="142" t="n"/>
+      <c r="D63" s="142" t="n"/>
+      <c r="E63" s="142" t="n"/>
+      <c r="F63" s="142" t="n"/>
     </row>
     <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="99" t="n"/>
-      <c r="B64" s="100" t="n"/>
-      <c r="C64" s="101" t="n"/>
-      <c r="D64" s="101" t="n"/>
-      <c r="E64" s="100" t="n"/>
-      <c r="F64" s="101" t="n"/>
+      <c r="A64" s="142" t="n"/>
+      <c r="B64" s="142" t="n"/>
+      <c r="C64" s="142" t="n"/>
+      <c r="D64" s="142" t="n"/>
+      <c r="E64" s="142" t="n"/>
+      <c r="F64" s="142" t="n"/>
     </row>
     <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="99" t="n"/>
-      <c r="B65" s="100" t="n"/>
-      <c r="C65" s="101" t="n"/>
-      <c r="D65" s="101" t="n"/>
-      <c r="E65" s="100" t="n"/>
-      <c r="F65" s="101" t="n"/>
+      <c r="A65" s="142" t="n"/>
+      <c r="B65" s="142" t="n"/>
+      <c r="C65" s="142" t="n"/>
+      <c r="D65" s="142" t="n"/>
+      <c r="E65" s="142" t="n"/>
+      <c r="F65" s="142" t="n"/>
     </row>
     <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="99" t="n"/>
-      <c r="B66" s="100" t="n"/>
-      <c r="C66" s="101" t="n"/>
-      <c r="D66" s="101" t="n"/>
-      <c r="E66" s="100" t="n"/>
-      <c r="F66" s="101" t="n"/>
+      <c r="A66" s="142" t="n"/>
+      <c r="B66" s="142" t="n"/>
+      <c r="C66" s="142" t="n"/>
+      <c r="D66" s="142" t="n"/>
+      <c r="E66" s="142" t="n"/>
+      <c r="F66" s="142" t="n"/>
     </row>
     <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="99" t="n"/>
-      <c r="B67" s="100" t="n"/>
-      <c r="C67" s="101" t="n"/>
-      <c r="D67" s="101" t="n"/>
-      <c r="E67" s="100" t="n"/>
-      <c r="F67" s="101" t="n"/>
+      <c r="A67" s="142" t="n"/>
+      <c r="B67" s="142" t="n"/>
+      <c r="C67" s="142" t="n"/>
+      <c r="D67" s="142" t="n"/>
+      <c r="E67" s="142" t="n"/>
+      <c r="F67" s="142" t="n"/>
     </row>
     <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="99" t="n"/>
-      <c r="B68" s="100" t="n"/>
-      <c r="C68" s="101" t="n"/>
-      <c r="D68" s="101" t="n"/>
-      <c r="E68" s="100" t="n"/>
-      <c r="F68" s="101" t="n"/>
-    </row>
-    <row r="69"/>
+      <c r="A68" s="142" t="n"/>
+      <c r="B68" s="142" t="n"/>
+      <c r="C68" s="142" t="n"/>
+      <c r="D68" s="142" t="n"/>
+      <c r="E68" s="142" t="n"/>
+      <c r="F68" s="142" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="142" t="n"/>
+      <c r="B69" s="142" t="n"/>
+      <c r="C69" s="142" t="n"/>
+      <c r="D69" s="142" t="n"/>
+      <c r="E69" s="142" t="n"/>
+      <c r="F69" s="142" t="n"/>
+    </row>
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="102" t="inlineStr">
         <is>
@@ -6613,142 +8232,149 @@
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="103" t="n"/>
-      <c r="B71" s="104" t="n"/>
-      <c r="C71" s="105" t="n"/>
-      <c r="D71" s="105" t="n"/>
-      <c r="E71" s="104" t="n"/>
-      <c r="F71" s="105" t="n"/>
+      <c r="A71" s="142" t="n"/>
+      <c r="B71" s="142" t="n"/>
+      <c r="C71" s="142" t="n"/>
+      <c r="D71" s="142" t="n"/>
+      <c r="E71" s="142" t="n"/>
+      <c r="F71" s="142" t="n"/>
     </row>
     <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="103" t="n"/>
-      <c r="B72" s="104" t="n"/>
-      <c r="C72" s="105" t="n"/>
-      <c r="D72" s="105" t="n"/>
-      <c r="E72" s="104" t="n"/>
-      <c r="F72" s="105" t="n"/>
+      <c r="A72" s="142" t="n"/>
+      <c r="B72" s="142" t="n"/>
+      <c r="C72" s="142" t="n"/>
+      <c r="D72" s="142" t="n"/>
+      <c r="E72" s="142" t="n"/>
+      <c r="F72" s="142" t="n"/>
     </row>
     <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="103" t="n"/>
-      <c r="B73" s="104" t="n"/>
-      <c r="C73" s="105" t="n"/>
-      <c r="D73" s="105" t="n"/>
-      <c r="E73" s="104" t="n"/>
-      <c r="F73" s="105" t="n"/>
+      <c r="A73" s="142" t="n"/>
+      <c r="B73" s="142" t="n"/>
+      <c r="C73" s="142" t="n"/>
+      <c r="D73" s="142" t="n"/>
+      <c r="E73" s="142" t="n"/>
+      <c r="F73" s="142" t="n"/>
     </row>
     <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="103" t="n"/>
-      <c r="B74" s="104" t="n"/>
-      <c r="C74" s="105" t="n"/>
-      <c r="D74" s="105" t="n"/>
-      <c r="E74" s="104" t="n"/>
-      <c r="F74" s="105" t="n"/>
+      <c r="A74" s="142" t="n"/>
+      <c r="B74" s="142" t="n"/>
+      <c r="C74" s="142" t="n"/>
+      <c r="D74" s="142" t="n"/>
+      <c r="E74" s="142" t="n"/>
+      <c r="F74" s="142" t="n"/>
     </row>
     <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="103" t="n"/>
-      <c r="B75" s="104" t="n"/>
-      <c r="C75" s="105" t="n"/>
-      <c r="D75" s="105" t="n"/>
-      <c r="E75" s="104" t="n"/>
-      <c r="F75" s="105" t="n"/>
+      <c r="A75" s="142" t="n"/>
+      <c r="B75" s="142" t="n"/>
+      <c r="C75" s="142" t="n"/>
+      <c r="D75" s="142" t="n"/>
+      <c r="E75" s="142" t="n"/>
+      <c r="F75" s="142" t="n"/>
     </row>
     <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="103" t="n"/>
-      <c r="B76" s="104" t="n"/>
-      <c r="C76" s="105" t="n"/>
-      <c r="D76" s="105" t="n"/>
-      <c r="E76" s="104" t="n"/>
-      <c r="F76" s="105" t="n"/>
+      <c r="A76" s="142" t="n"/>
+      <c r="B76" s="142" t="n"/>
+      <c r="C76" s="142" t="n"/>
+      <c r="D76" s="142" t="n"/>
+      <c r="E76" s="142" t="n"/>
+      <c r="F76" s="142" t="n"/>
     </row>
     <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="103" t="n"/>
-      <c r="B77" s="104" t="n"/>
-      <c r="C77" s="105" t="n"/>
-      <c r="D77" s="105" t="n"/>
-      <c r="E77" s="104" t="n"/>
-      <c r="F77" s="105" t="n"/>
+      <c r="A77" s="142" t="n"/>
+      <c r="B77" s="142" t="n"/>
+      <c r="C77" s="142" t="n"/>
+      <c r="D77" s="142" t="n"/>
+      <c r="E77" s="142" t="n"/>
+      <c r="F77" s="142" t="n"/>
     </row>
     <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="103" t="n"/>
-      <c r="B78" s="104" t="n"/>
-      <c r="C78" s="105" t="n"/>
-      <c r="D78" s="105" t="n"/>
-      <c r="E78" s="104" t="n"/>
-      <c r="F78" s="105" t="n"/>
+      <c r="A78" s="142" t="n"/>
+      <c r="B78" s="142" t="n"/>
+      <c r="C78" s="142" t="n"/>
+      <c r="D78" s="142" t="n"/>
+      <c r="E78" s="142" t="n"/>
+      <c r="F78" s="142" t="n"/>
     </row>
     <row r="79" ht="20" customHeight="1">
-      <c r="A79" s="103" t="n"/>
-      <c r="B79" s="104" t="n"/>
-      <c r="C79" s="105" t="n"/>
-      <c r="D79" s="105" t="n"/>
-      <c r="E79" s="104" t="n"/>
-      <c r="F79" s="105" t="n"/>
+      <c r="A79" s="142" t="n"/>
+      <c r="B79" s="142" t="n"/>
+      <c r="C79" s="142" t="n"/>
+      <c r="D79" s="142" t="n"/>
+      <c r="E79" s="142" t="n"/>
+      <c r="F79" s="142" t="n"/>
     </row>
     <row r="80" ht="20" customHeight="1">
-      <c r="A80" s="103" t="n"/>
-      <c r="B80" s="104" t="n"/>
-      <c r="C80" s="105" t="n"/>
-      <c r="D80" s="105" t="n"/>
-      <c r="E80" s="104" t="n"/>
-      <c r="F80" s="105" t="n"/>
+      <c r="A80" s="142" t="n"/>
+      <c r="B80" s="142" t="n"/>
+      <c r="C80" s="142" t="n"/>
+      <c r="D80" s="142" t="n"/>
+      <c r="E80" s="142" t="n"/>
+      <c r="F80" s="142" t="n"/>
     </row>
     <row r="81" ht="20" customHeight="1">
-      <c r="A81" s="103" t="n"/>
-      <c r="B81" s="104" t="n"/>
-      <c r="C81" s="105" t="n"/>
-      <c r="D81" s="105" t="n"/>
-      <c r="E81" s="104" t="n"/>
-      <c r="F81" s="105" t="n"/>
+      <c r="A81" s="142" t="n"/>
+      <c r="B81" s="142" t="n"/>
+      <c r="C81" s="142" t="n"/>
+      <c r="D81" s="142" t="n"/>
+      <c r="E81" s="142" t="n"/>
+      <c r="F81" s="142" t="n"/>
     </row>
     <row r="82" ht="20" customHeight="1">
-      <c r="A82" s="103" t="n"/>
-      <c r="B82" s="104" t="n"/>
-      <c r="C82" s="105" t="n"/>
-      <c r="D82" s="105" t="n"/>
-      <c r="E82" s="104" t="n"/>
-      <c r="F82" s="105" t="n"/>
+      <c r="A82" s="142" t="n"/>
+      <c r="B82" s="142" t="n"/>
+      <c r="C82" s="142" t="n"/>
+      <c r="D82" s="142" t="n"/>
+      <c r="E82" s="142" t="n"/>
+      <c r="F82" s="142" t="n"/>
     </row>
     <row r="83" ht="20" customHeight="1">
-      <c r="A83" s="103" t="n"/>
-      <c r="B83" s="104" t="n"/>
-      <c r="C83" s="105" t="n"/>
-      <c r="D83" s="105" t="n"/>
-      <c r="E83" s="104" t="n"/>
-      <c r="F83" s="105" t="n"/>
+      <c r="A83" s="142" t="n"/>
+      <c r="B83" s="142" t="n"/>
+      <c r="C83" s="142" t="n"/>
+      <c r="D83" s="142" t="n"/>
+      <c r="E83" s="142" t="n"/>
+      <c r="F83" s="142" t="n"/>
     </row>
     <row r="84" ht="20" customHeight="1">
-      <c r="A84" s="103" t="n"/>
-      <c r="B84" s="104" t="n"/>
-      <c r="C84" s="105" t="n"/>
-      <c r="D84" s="105" t="n"/>
-      <c r="E84" s="104" t="n"/>
-      <c r="F84" s="105" t="n"/>
+      <c r="A84" s="142" t="n"/>
+      <c r="B84" s="142" t="n"/>
+      <c r="C84" s="142" t="n"/>
+      <c r="D84" s="142" t="n"/>
+      <c r="E84" s="142" t="n"/>
+      <c r="F84" s="142" t="n"/>
     </row>
     <row r="85" ht="20" customHeight="1">
-      <c r="A85" s="103" t="n"/>
-      <c r="B85" s="104" t="n"/>
-      <c r="C85" s="105" t="n"/>
-      <c r="D85" s="105" t="n"/>
-      <c r="E85" s="104" t="n"/>
-      <c r="F85" s="105" t="n"/>
+      <c r="A85" s="142" t="n"/>
+      <c r="B85" s="142" t="n"/>
+      <c r="C85" s="142" t="n"/>
+      <c r="D85" s="142" t="n"/>
+      <c r="E85" s="142" t="n"/>
+      <c r="F85" s="142" t="n"/>
     </row>
     <row r="86" ht="20" customHeight="1">
-      <c r="A86" s="103" t="n"/>
-      <c r="B86" s="104" t="n"/>
-      <c r="C86" s="105" t="n"/>
-      <c r="D86" s="105" t="n"/>
-      <c r="E86" s="104" t="n"/>
-      <c r="F86" s="105" t="n"/>
+      <c r="A86" s="142" t="n"/>
+      <c r="B86" s="142" t="n"/>
+      <c r="C86" s="142" t="n"/>
+      <c r="D86" s="142" t="n"/>
+      <c r="E86" s="142" t="n"/>
+      <c r="F86" s="142" t="n"/>
     </row>
     <row r="87" ht="20" customHeight="1">
-      <c r="A87" s="103" t="n"/>
-      <c r="B87" s="104" t="n"/>
-      <c r="C87" s="105" t="n"/>
-      <c r="D87" s="105" t="n"/>
-      <c r="E87" s="104" t="n"/>
-      <c r="F87" s="105" t="n"/>
-    </row>
-    <row r="88"/>
+      <c r="A87" s="142" t="n"/>
+      <c r="B87" s="142" t="n"/>
+      <c r="C87" s="142" t="n"/>
+      <c r="D87" s="142" t="n"/>
+      <c r="E87" s="142" t="n"/>
+      <c r="F87" s="142" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="142" t="n"/>
+      <c r="B88" s="142" t="n"/>
+      <c r="C88" s="142" t="n"/>
+      <c r="D88" s="142" t="n"/>
+      <c r="E88" s="142" t="n"/>
+      <c r="F88" s="142" t="n"/>
+    </row>
     <row r="89" ht="18" customHeight="1">
       <c r="A89" s="106" t="inlineStr">
         <is>
@@ -6757,36 +8383,36 @@
       </c>
     </row>
     <row r="90" ht="52" customHeight="1">
-      <c r="A90" s="107" t="n"/>
-      <c r="B90" s="108" t="n"/>
-      <c r="C90" s="108" t="n"/>
-      <c r="D90" s="108" t="n"/>
-      <c r="E90" s="108" t="n"/>
-      <c r="F90" s="108" t="n"/>
+      <c r="A90" s="142" t="n"/>
+      <c r="B90" s="142" t="n"/>
+      <c r="C90" s="142" t="n"/>
+      <c r="D90" s="142" t="n"/>
+      <c r="E90" s="142" t="n"/>
+      <c r="F90" s="142" t="n"/>
     </row>
     <row r="91" ht="52" customHeight="1">
-      <c r="A91" s="107" t="n"/>
-      <c r="B91" s="108" t="n"/>
-      <c r="C91" s="108" t="n"/>
-      <c r="D91" s="108" t="n"/>
-      <c r="E91" s="108" t="n"/>
-      <c r="F91" s="108" t="n"/>
+      <c r="A91" s="142" t="n"/>
+      <c r="B91" s="142" t="n"/>
+      <c r="C91" s="142" t="n"/>
+      <c r="D91" s="142" t="n"/>
+      <c r="E91" s="142" t="n"/>
+      <c r="F91" s="142" t="n"/>
     </row>
     <row r="92" ht="52" customHeight="1">
-      <c r="A92" s="107" t="n"/>
-      <c r="B92" s="108" t="n"/>
-      <c r="C92" s="108" t="n"/>
-      <c r="D92" s="108" t="n"/>
-      <c r="E92" s="108" t="n"/>
-      <c r="F92" s="108" t="n"/>
+      <c r="A92" s="142" t="n"/>
+      <c r="B92" s="142" t="n"/>
+      <c r="C92" s="142" t="n"/>
+      <c r="D92" s="142" t="n"/>
+      <c r="E92" s="142" t="n"/>
+      <c r="F92" s="142" t="n"/>
     </row>
     <row r="93" ht="52" customHeight="1">
-      <c r="A93" s="107" t="n"/>
-      <c r="B93" s="108" t="n"/>
-      <c r="C93" s="108" t="n"/>
-      <c r="D93" s="108" t="n"/>
-      <c r="E93" s="108" t="n"/>
-      <c r="F93" s="108" t="n"/>
+      <c r="A93" s="142" t="n"/>
+      <c r="B93" s="142" t="n"/>
+      <c r="C93" s="142" t="n"/>
+      <c r="D93" s="142" t="n"/>
+      <c r="E93" s="142" t="n"/>
+      <c r="F93" s="142" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -6801,510 +8427,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="38" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="35" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="80" t="inlineStr">
-        <is>
-          <t>Registro Chiarimenti — Stato e Impatto sulla Stima</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="81" t="inlineStr">
-        <is>
-          <t>Domande da inviare entro 29/04/2026 ore 12:00 | Ordinate per 'Bloccante per stima' decrescente</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="109" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B3" s="109" t="inlineStr">
-        <is>
-          <t>Capability</t>
-        </is>
-      </c>
-      <c r="C3" s="109" t="inlineStr">
-        <is>
-          <t>Categoria</t>
-        </is>
-      </c>
-      <c r="D3" s="109" t="inlineStr">
-        <is>
-          <t>Testo Domanda</t>
-        </is>
-      </c>
-      <c r="E3" s="109" t="inlineStr">
-        <is>
-          <t>Driver che abilita</t>
-        </is>
-      </c>
-      <c r="F3" s="109" t="inlineStr">
-        <is>
-          <t>Prio</t>
-        </is>
-      </c>
-      <c r="G3" s="109" t="inlineStr">
-        <is>
-          <t>Stato</t>
-        </is>
-      </c>
-      <c r="H3" s="109" t="inlineStr">
-        <is>
-          <t>Data Risposta</t>
-        </is>
-      </c>
-      <c r="I3" s="109" t="inlineStr">
-        <is>
-          <t>Sintesi Risposta RAI</t>
-        </is>
-      </c>
-      <c r="J3" s="109" t="inlineStr">
-        <is>
-          <t>Impatto se non risolto</t>
-        </is>
-      </c>
-      <c r="K3" s="109" t="inlineStr">
-        <is>
-          <t>Bloccante per stima</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="40" customHeight="1">
-      <c r="A4" s="110" t="n"/>
-      <c r="B4" s="111" t="n"/>
-      <c r="C4" s="112" t="n"/>
-      <c r="D4" s="49" t="n"/>
-      <c r="E4" s="49" t="n"/>
-      <c r="F4" s="110" t="n"/>
-      <c r="G4" s="113" t="n"/>
-      <c r="H4" s="114" t="n"/>
-      <c r="I4" s="49" t="n"/>
-      <c r="J4" s="115" t="n"/>
-      <c r="K4" s="116" t="n"/>
-    </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" s="110" t="n"/>
-      <c r="B5" s="111" t="n"/>
-      <c r="C5" s="112" t="n"/>
-      <c r="D5" s="49" t="n"/>
-      <c r="E5" s="49" t="n"/>
-      <c r="F5" s="110" t="n"/>
-      <c r="G5" s="113" t="n"/>
-      <c r="H5" s="114" t="n"/>
-      <c r="I5" s="49" t="n"/>
-      <c r="J5" s="115" t="n"/>
-      <c r="K5" s="116" t="n"/>
-    </row>
-    <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="110" t="n"/>
-      <c r="B6" s="111" t="n"/>
-      <c r="C6" s="112" t="n"/>
-      <c r="D6" s="49" t="n"/>
-      <c r="E6" s="49" t="n"/>
-      <c r="F6" s="110" t="n"/>
-      <c r="G6" s="113" t="n"/>
-      <c r="H6" s="114" t="n"/>
-      <c r="I6" s="49" t="n"/>
-      <c r="J6" s="115" t="n"/>
-      <c r="K6" s="116" t="n"/>
-    </row>
-    <row r="7" ht="40" customHeight="1">
-      <c r="A7" s="110" t="n"/>
-      <c r="B7" s="111" t="n"/>
-      <c r="C7" s="112" t="n"/>
-      <c r="D7" s="49" t="n"/>
-      <c r="E7" s="49" t="n"/>
-      <c r="F7" s="110" t="n"/>
-      <c r="G7" s="113" t="n"/>
-      <c r="H7" s="114" t="n"/>
-      <c r="I7" s="49" t="n"/>
-      <c r="J7" s="115" t="n"/>
-      <c r="K7" s="116" t="n"/>
-    </row>
-    <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="110" t="n"/>
-      <c r="B8" s="111" t="n"/>
-      <c r="C8" s="112" t="n"/>
-      <c r="D8" s="49" t="n"/>
-      <c r="E8" s="49" t="n"/>
-      <c r="F8" s="110" t="n"/>
-      <c r="G8" s="113" t="n"/>
-      <c r="H8" s="114" t="n"/>
-      <c r="I8" s="49" t="n"/>
-      <c r="J8" s="115" t="n"/>
-      <c r="K8" s="116" t="n"/>
-    </row>
-    <row r="9" ht="40" customHeight="1">
-      <c r="A9" s="110" t="n"/>
-      <c r="B9" s="111" t="n"/>
-      <c r="C9" s="112" t="n"/>
-      <c r="D9" s="49" t="n"/>
-      <c r="E9" s="49" t="n"/>
-      <c r="F9" s="110" t="n"/>
-      <c r="G9" s="113" t="n"/>
-      <c r="H9" s="114" t="n"/>
-      <c r="I9" s="49" t="n"/>
-      <c r="J9" s="115" t="n"/>
-      <c r="K9" s="116" t="n"/>
-    </row>
-    <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="110" t="n"/>
-      <c r="B10" s="111" t="n"/>
-      <c r="C10" s="112" t="n"/>
-      <c r="D10" s="49" t="n"/>
-      <c r="E10" s="49" t="n"/>
-      <c r="F10" s="110" t="n"/>
-      <c r="G10" s="113" t="n"/>
-      <c r="H10" s="114" t="n"/>
-      <c r="I10" s="49" t="n"/>
-      <c r="J10" s="115" t="n"/>
-      <c r="K10" s="116" t="n"/>
-    </row>
-    <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="110" t="n"/>
-      <c r="B11" s="111" t="n"/>
-      <c r="C11" s="112" t="n"/>
-      <c r="D11" s="49" t="n"/>
-      <c r="E11" s="49" t="n"/>
-      <c r="F11" s="110" t="n"/>
-      <c r="G11" s="113" t="n"/>
-      <c r="H11" s="114" t="n"/>
-      <c r="I11" s="49" t="n"/>
-      <c r="J11" s="115" t="n"/>
-      <c r="K11" s="116" t="n"/>
-    </row>
-    <row r="12" ht="40" customHeight="1">
-      <c r="A12" s="110" t="n"/>
-      <c r="B12" s="111" t="n"/>
-      <c r="C12" s="112" t="n"/>
-      <c r="D12" s="49" t="n"/>
-      <c r="E12" s="49" t="n"/>
-      <c r="F12" s="110" t="n"/>
-      <c r="G12" s="113" t="n"/>
-      <c r="H12" s="114" t="n"/>
-      <c r="I12" s="49" t="n"/>
-      <c r="J12" s="115" t="n"/>
-      <c r="K12" s="116" t="n"/>
-    </row>
-    <row r="13" ht="40" customHeight="1">
-      <c r="A13" s="110" t="n"/>
-      <c r="B13" s="111" t="n"/>
-      <c r="C13" s="112" t="n"/>
-      <c r="D13" s="49" t="n"/>
-      <c r="E13" s="49" t="n"/>
-      <c r="F13" s="110" t="n"/>
-      <c r="G13" s="113" t="n"/>
-      <c r="H13" s="114" t="n"/>
-      <c r="I13" s="49" t="n"/>
-      <c r="J13" s="115" t="n"/>
-      <c r="K13" s="116" t="n"/>
-    </row>
-    <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="110" t="n"/>
-      <c r="B14" s="111" t="n"/>
-      <c r="C14" s="112" t="n"/>
-      <c r="D14" s="49" t="n"/>
-      <c r="E14" s="49" t="n"/>
-      <c r="F14" s="110" t="n"/>
-      <c r="G14" s="113" t="n"/>
-      <c r="H14" s="114" t="n"/>
-      <c r="I14" s="49" t="n"/>
-      <c r="J14" s="115" t="n"/>
-      <c r="K14" s="116" t="n"/>
-    </row>
-    <row r="15" ht="40" customHeight="1">
-      <c r="A15" s="110" t="n"/>
-      <c r="B15" s="111" t="n"/>
-      <c r="C15" s="112" t="n"/>
-      <c r="D15" s="49" t="n"/>
-      <c r="E15" s="49" t="n"/>
-      <c r="F15" s="110" t="n"/>
-      <c r="G15" s="113" t="n"/>
-      <c r="H15" s="114" t="n"/>
-      <c r="I15" s="49" t="n"/>
-      <c r="J15" s="115" t="n"/>
-      <c r="K15" s="116" t="n"/>
-    </row>
-    <row r="16" ht="40" customHeight="1">
-      <c r="A16" s="110" t="n"/>
-      <c r="B16" s="111" t="n"/>
-      <c r="C16" s="112" t="n"/>
-      <c r="D16" s="49" t="n"/>
-      <c r="E16" s="49" t="n"/>
-      <c r="F16" s="110" t="n"/>
-      <c r="G16" s="113" t="n"/>
-      <c r="H16" s="114" t="n"/>
-      <c r="I16" s="49" t="n"/>
-      <c r="J16" s="115" t="n"/>
-      <c r="K16" s="116" t="n"/>
-    </row>
-    <row r="17" ht="40" customHeight="1">
-      <c r="A17" s="110" t="n"/>
-      <c r="B17" s="111" t="n"/>
-      <c r="C17" s="112" t="n"/>
-      <c r="D17" s="49" t="n"/>
-      <c r="E17" s="49" t="n"/>
-      <c r="F17" s="110" t="n"/>
-      <c r="G17" s="113" t="n"/>
-      <c r="H17" s="114" t="n"/>
-      <c r="I17" s="49" t="n"/>
-      <c r="J17" s="115" t="n"/>
-      <c r="K17" s="116" t="n"/>
-    </row>
-    <row r="18" ht="40" customHeight="1">
-      <c r="A18" s="110" t="n"/>
-      <c r="B18" s="111" t="n"/>
-      <c r="C18" s="112" t="n"/>
-      <c r="D18" s="49" t="n"/>
-      <c r="E18" s="49" t="n"/>
-      <c r="F18" s="110" t="n"/>
-      <c r="G18" s="113" t="n"/>
-      <c r="H18" s="114" t="n"/>
-      <c r="I18" s="49" t="n"/>
-      <c r="J18" s="115" t="n"/>
-      <c r="K18" s="116" t="n"/>
-    </row>
-    <row r="19" ht="40" customHeight="1">
-      <c r="A19" s="110" t="n"/>
-      <c r="B19" s="111" t="n"/>
-      <c r="C19" s="112" t="n"/>
-      <c r="D19" s="49" t="n"/>
-      <c r="E19" s="49" t="n"/>
-      <c r="F19" s="110" t="n"/>
-      <c r="G19" s="113" t="n"/>
-      <c r="H19" s="114" t="n"/>
-      <c r="I19" s="49" t="n"/>
-      <c r="J19" s="117" t="n"/>
-      <c r="K19" s="118" t="n"/>
-    </row>
-    <row r="20" ht="40" customHeight="1">
-      <c r="A20" s="110" t="n"/>
-      <c r="B20" s="111" t="n"/>
-      <c r="C20" s="112" t="n"/>
-      <c r="D20" s="49" t="n"/>
-      <c r="E20" s="49" t="n"/>
-      <c r="F20" s="110" t="n"/>
-      <c r="G20" s="113" t="n"/>
-      <c r="H20" s="114" t="n"/>
-      <c r="I20" s="49" t="n"/>
-      <c r="J20" s="117" t="n"/>
-      <c r="K20" s="118" t="n"/>
-    </row>
-    <row r="21" ht="40" customHeight="1">
-      <c r="A21" s="110" t="n"/>
-      <c r="B21" s="111" t="n"/>
-      <c r="C21" s="112" t="n"/>
-      <c r="D21" s="49" t="n"/>
-      <c r="E21" s="49" t="n"/>
-      <c r="F21" s="110" t="n"/>
-      <c r="G21" s="113" t="n"/>
-      <c r="H21" s="114" t="n"/>
-      <c r="I21" s="49" t="n"/>
-      <c r="J21" s="117" t="n"/>
-      <c r="K21" s="118" t="n"/>
-    </row>
-    <row r="22" ht="40" customHeight="1">
-      <c r="A22" s="110" t="n"/>
-      <c r="B22" s="111" t="n"/>
-      <c r="C22" s="112" t="n"/>
-      <c r="D22" s="49" t="n"/>
-      <c r="E22" s="49" t="n"/>
-      <c r="F22" s="110" t="n"/>
-      <c r="G22" s="113" t="n"/>
-      <c r="H22" s="114" t="n"/>
-      <c r="I22" s="49" t="n"/>
-      <c r="J22" s="117" t="n"/>
-      <c r="K22" s="118" t="n"/>
-    </row>
-    <row r="23" ht="40" customHeight="1">
-      <c r="A23" s="110" t="n"/>
-      <c r="B23" s="111" t="n"/>
-      <c r="C23" s="112" t="n"/>
-      <c r="D23" s="49" t="n"/>
-      <c r="E23" s="49" t="n"/>
-      <c r="F23" s="110" t="n"/>
-      <c r="G23" s="113" t="n"/>
-      <c r="H23" s="114" t="n"/>
-      <c r="I23" s="49" t="n"/>
-      <c r="J23" s="117" t="n"/>
-      <c r="K23" s="118" t="n"/>
-    </row>
-    <row r="24" ht="40" customHeight="1">
-      <c r="A24" s="110" t="n"/>
-      <c r="B24" s="111" t="n"/>
-      <c r="C24" s="112" t="n"/>
-      <c r="D24" s="49" t="n"/>
-      <c r="E24" s="49" t="n"/>
-      <c r="F24" s="110" t="n"/>
-      <c r="G24" s="113" t="n"/>
-      <c r="H24" s="114" t="n"/>
-      <c r="I24" s="49" t="n"/>
-      <c r="J24" s="117" t="n"/>
-      <c r="K24" s="118" t="n"/>
-    </row>
-    <row r="25" ht="40" customHeight="1">
-      <c r="A25" s="110" t="n"/>
-      <c r="B25" s="111" t="n"/>
-      <c r="C25" s="112" t="n"/>
-      <c r="D25" s="49" t="n"/>
-      <c r="E25" s="49" t="n"/>
-      <c r="F25" s="110" t="n"/>
-      <c r="G25" s="113" t="n"/>
-      <c r="H25" s="114" t="n"/>
-      <c r="I25" s="49" t="n"/>
-      <c r="J25" s="117" t="n"/>
-      <c r="K25" s="118" t="n"/>
-    </row>
-    <row r="26" ht="40" customHeight="1">
-      <c r="A26" s="110" t="n"/>
-      <c r="B26" s="111" t="n"/>
-      <c r="C26" s="112" t="n"/>
-      <c r="D26" s="49" t="n"/>
-      <c r="E26" s="49" t="n"/>
-      <c r="F26" s="110" t="n"/>
-      <c r="G26" s="113" t="n"/>
-      <c r="H26" s="114" t="n"/>
-      <c r="I26" s="49" t="n"/>
-      <c r="J26" s="117" t="n"/>
-      <c r="K26" s="118" t="n"/>
-    </row>
-    <row r="27" ht="40" customHeight="1">
-      <c r="A27" s="110" t="n"/>
-      <c r="B27" s="111" t="n"/>
-      <c r="C27" s="112" t="n"/>
-      <c r="D27" s="49" t="n"/>
-      <c r="E27" s="49" t="n"/>
-      <c r="F27" s="110" t="n"/>
-      <c r="G27" s="113" t="n"/>
-      <c r="H27" s="114" t="n"/>
-      <c r="I27" s="49" t="n"/>
-      <c r="J27" s="117" t="n"/>
-      <c r="K27" s="118" t="n"/>
-    </row>
-    <row r="28" ht="40" customHeight="1">
-      <c r="A28" s="110" t="n"/>
-      <c r="B28" s="111" t="n"/>
-      <c r="C28" s="112" t="n"/>
-      <c r="D28" s="49" t="n"/>
-      <c r="E28" s="49" t="n"/>
-      <c r="F28" s="110" t="n"/>
-      <c r="G28" s="113" t="n"/>
-      <c r="H28" s="114" t="n"/>
-      <c r="I28" s="49" t="n"/>
-      <c r="J28" s="117" t="n"/>
-      <c r="K28" s="118" t="n"/>
-    </row>
-    <row r="29" ht="40" customHeight="1">
-      <c r="A29" s="110" t="n"/>
-      <c r="B29" s="111" t="n"/>
-      <c r="C29" s="112" t="n"/>
-      <c r="D29" s="49" t="n"/>
-      <c r="E29" s="49" t="n"/>
-      <c r="F29" s="110" t="n"/>
-      <c r="G29" s="113" t="n"/>
-      <c r="H29" s="114" t="n"/>
-      <c r="I29" s="49" t="n"/>
-      <c r="J29" s="117" t="n"/>
-      <c r="K29" s="118" t="n"/>
-    </row>
-    <row r="30" ht="40" customHeight="1">
-      <c r="A30" s="110" t="n"/>
-      <c r="B30" s="111" t="n"/>
-      <c r="C30" s="112" t="n"/>
-      <c r="D30" s="49" t="n"/>
-      <c r="E30" s="49" t="n"/>
-      <c r="F30" s="110" t="n"/>
-      <c r="G30" s="113" t="n"/>
-      <c r="H30" s="114" t="n"/>
-      <c r="I30" s="49" t="n"/>
-      <c r="J30" s="117" t="n"/>
-      <c r="K30" s="118" t="n"/>
-    </row>
-    <row r="31" ht="40" customHeight="1">
-      <c r="A31" s="110" t="n"/>
-      <c r="B31" s="111" t="n"/>
-      <c r="C31" s="112" t="n"/>
-      <c r="D31" s="49" t="n"/>
-      <c r="E31" s="49" t="n"/>
-      <c r="F31" s="110" t="n"/>
-      <c r="G31" s="113" t="n"/>
-      <c r="H31" s="114" t="n"/>
-      <c r="I31" s="49" t="n"/>
-      <c r="J31" s="113" t="n"/>
-      <c r="K31" s="118" t="n"/>
-    </row>
-    <row r="32" ht="40" customHeight="1">
-      <c r="A32" s="110" t="n"/>
-      <c r="B32" s="111" t="n"/>
-      <c r="C32" s="112" t="n"/>
-      <c r="D32" s="49" t="n"/>
-      <c r="E32" s="49" t="n"/>
-      <c r="F32" s="110" t="n"/>
-      <c r="G32" s="113" t="n"/>
-      <c r="H32" s="114" t="n"/>
-      <c r="I32" s="49" t="n"/>
-      <c r="J32" s="113" t="n"/>
-      <c r="K32" s="118" t="n"/>
-    </row>
-    <row r="33" ht="40" customHeight="1">
-      <c r="A33" s="110" t="n"/>
-      <c r="B33" s="111" t="n"/>
-      <c r="C33" s="112" t="n"/>
-      <c r="D33" s="49" t="n"/>
-      <c r="E33" s="49" t="n"/>
-      <c r="F33" s="110" t="n"/>
-      <c r="G33" s="113" t="n"/>
-      <c r="H33" s="114" t="n"/>
-      <c r="I33" s="49" t="n"/>
-      <c r="J33" s="113" t="n"/>
-      <c r="K33" s="118" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A1:L1"/>
-  </mergeCells>
-  <dataValidations count="4">
-    <dataValidation sqref="F4:F200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valore non ammesso" error="Valore non ammesso" type="list">
-      <formula1>"1,2,3"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G4:G200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valore non ammesso" error="Valore non ammesso" type="list">
-      <formula1>"Non inviato,Inviato,Risposta ricevuta"</formula1>
-    </dataValidation>
-    <dataValidation sqref="J4:J200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valore non ammesso" error="Valore non ammesso" type="list">
-      <formula1>"ALTO,MEDIO,BASSO"</formula1>
-    </dataValidation>
-    <dataValidation sqref="K4:K200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valore non ammesso" error="Valore non ammesso" type="list">
-      <formula1>"SI,NO"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>